--- a/zhongkao_vocab.xlsx
+++ b/zhongkao_vocab.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2822"/>
+  <dimension ref="A1:F2821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>中文释义</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>中文释义(精简)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2489,7 +2494,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>英[ˈtʃɪldrən] 美[ˈtʃɪldrən]</t>
+          <t>ˈtʃɪldrən</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3239,7 +3244,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>英[θæŋks] 美[θæŋks]</t>
+          <t>θæŋks</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3569,7 +3574,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>英[ɪɡˈzæktli] 美[ɪɡˈzæktli]</t>
+          <t>ɪɡˈzæktli</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4494,7 +4499,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>英[lɒst] 美[lɔːst]</t>
+          <t>lɒst lɔːst</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5689,7 +5694,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>英[ˈdɪfrənt] 美[ˈdɪfrənt]</t>
+          <t>ˈdɪfrənt</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -7369,7 +7374,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>英[baɪ] 美[baɪ]</t>
+          <t>baɪ</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -10759,7 +10764,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>英[mɪs] 美[mɪs]</t>
+          <t>mɪs</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11659,7 +11664,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>英[ˈmuːvɪŋ] 美[ˈmuːvɪŋ]</t>
+          <t>ˈmuːvɪŋ</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -15494,7 +15499,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>英[ˈfəʊtəʊ] 美[ˈfoʊtoʊ]</t>
+          <t>ˈfəʊtəʊ ˈfoʊtoʊ</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -16004,7 +16009,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>英[ˈɪŋɡlənd] 美[ˈɪŋɡlənd]</t>
+          <t>ˈɪŋɡlənd</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -17114,7 +17119,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>英[ˈdʒɜːmən] 美[ˈdʒɜːrmən]</t>
+          <t>ˈdʒɜːmən ˈdʒɜːrmən</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -18134,7 +18139,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>英[ˌtʃaɪˈniːz] 美[ˌtʃaɪˈniːz]</t>
+          <t>ˌtʃaɪˈniːz</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -18284,7 +18289,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>英[ˈɜ:lɪə(r)] 美[ˈɜːrliər]</t>
+          <t>ˈɜ:lɪə(r) ˈɜːrliər</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -19449,7 +19454,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>英[ˈɡrænpɑː] 美[ˈɡrænpɑː]</t>
+          <t>ˈɡrænpɑː</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -19684,7 +19689,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>英[ɪkˈsaɪtɪd] 美[ɪkˈsaɪtɪd]</t>
+          <t>ɪkˈsaɪtɪd</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -20099,7 +20104,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>英[ˈtɜːnɪŋ] 美[ˈtɜːrnɪŋ]</t>
+          <t>ˈtɜːnɪŋ ˈtɜːrnɪŋ</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -20699,7 +20704,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>英[ˈsləʊli] 美[ˈsloʊli]</t>
+          <t>ˈsləʊli ˈsloʊli</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -20789,7 +20794,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>英[ˈrʌʃ(ə)n] 美[ˈrʌʃ(ə)n]</t>
+          <t>ˈrʌʃ(ə)n</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -22259,7 +22264,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>英[ˈɪŋɡlɪʃ] 美[ˈɪŋɡlɪʃ]</t>
+          <t>ˈɪŋɡlɪʃ</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -23939,7 +23944,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>英[əˈmerɪkə] 美[əˈmerɪkə]</t>
+          <t>əˈmerɪkə</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -24509,7 +24514,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>英[ˈɡrænmɑː] 美[ˈɡrænmɑː]</t>
+          <t>ˈɡrænmɑː</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -24899,7 +24904,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>英[kəmˈpjuːtə(r)] 美[kəmˈpjuːtər]</t>
+          <t>kəmˈpjuːtə(r) kəmˈpjuːtər</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -26729,7 +26734,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>英[ˈbrɪtɪʃ] 美[ˈbrɪtɪʃ]</t>
+          <t>ˈbrɪtɪʃ</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
@@ -27149,7 +27154,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>英[ˈsɪli] 美[ˈsɪli]</t>
+          <t>ˈsɪli</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -27804,7 +27809,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>英[frɑːns] 美[fræns]</t>
+          <t>frɑːns fræns</t>
         </is>
       </c>
       <c r="D915" t="inlineStr">
@@ -28794,7 +28799,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>英[ˈlʌndən] 美[ˈlʌndən]</t>
+          <t>ˈlʌndən</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
@@ -28974,7 +28979,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>英[frentʃ] 美[frentʃ]</t>
+          <t>frentʃ</t>
         </is>
       </c>
       <c r="D954" t="inlineStr">
@@ -29274,7 +29279,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>英[fænˈtæstɪk] 美[fænˈtæstɪk]</t>
+          <t>fænˈtæstɪk</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
@@ -29574,7 +29579,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>英[ˈbrəʊkən] 美[ˈbroʊkən]</t>
+          <t>ˈbrəʊkən ˈbroʊkən</t>
         </is>
       </c>
       <c r="E974" t="inlineStr">
@@ -30319,7 +30324,7 @@
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>英[kləʊzd] 美[kloʊzd]</t>
+          <t>kləʊzd kloʊzd</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -30764,7 +30769,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>英[ˈhevɪli] 美[ˈhevɪli]</t>
+          <t>ˈhevɪli</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
@@ -30854,7 +30859,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>英[ˈsʌmdeɪ] 美[ˈsʌmdeɪ]</t>
+          <t>ˈsʌmdeɪ</t>
         </is>
       </c>
       <c r="D1017" t="inlineStr">
@@ -30914,7 +30919,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>英[ˌdʒæpəˈniːz] 美[ˌdʒæpəˈniːz]</t>
+          <t>ˌdʒæpəˈniːz</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
@@ -31394,7 +31399,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>英[ˈbrɪt(ə)n] 美[ˈbrɪt(ə)n]</t>
+          <t>ˈbrɪt(ə)n</t>
         </is>
       </c>
       <c r="D1035" t="inlineStr">
@@ -33644,7 +33649,7 @@
       </c>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>英[ˈkænədə] 美[ˈkænədə]</t>
+          <t>ˈkænədə</t>
         </is>
       </c>
       <c r="D1110" t="inlineStr">
@@ -33674,7 +33679,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>英[ˈtʃaɪnə] 美[ˈtʃaɪnə]</t>
+          <t>ˈtʃaɪnə</t>
         </is>
       </c>
       <c r="D1111" t="inlineStr">
@@ -34274,7 +34279,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>英[ˈskɒtlənd] 美[ˈskɑːtlənd]</t>
+          <t>ˈskɒtlənd ˈskɑːtlənd</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
@@ -34484,7 +34489,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>英[ˈɪndiə] 美[ˈɪndiə]</t>
+          <t>ˈɪndiə</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
@@ -34544,7 +34549,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>英[æd] 美[æd]</t>
+          <t>æd</t>
         </is>
       </c>
       <c r="D1140" t="inlineStr">
@@ -34574,7 +34579,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>英[ˌθæŋksˈɡɪvɪŋ] 美[ˌθæŋksˈɡɪvɪŋ]</t>
+          <t>ˌθæŋksˈɡɪvɪŋ</t>
         </is>
       </c>
       <c r="D1141" t="inlineStr">
@@ -34604,7 +34609,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>英[ˈmʌmi] 美[ˈmʌmi]</t>
+          <t>ˈmʌmi</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
@@ -34634,7 +34639,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>英[ˈɡræni] 美[ˈɡræni]</t>
+          <t>ˈɡræni</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
@@ -35169,7 +35174,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>英[kəʊk] 美[koʊk]</t>
+          <t>kəʊk koʊk</t>
         </is>
       </c>
       <c r="D1161" t="inlineStr">
@@ -35589,7 +35594,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>英[ɪˈtæliən] 美[ɪˈtæliən]</t>
+          <t>ɪˈtæliən</t>
         </is>
       </c>
       <c r="D1175" t="inlineStr">
@@ -35649,7 +35654,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>英[ˈfeɪvərɪt] 美[ˈfeɪvərɪt]</t>
+          <t>ˈfeɪvərɪt</t>
         </is>
       </c>
       <c r="D1177" t="inlineStr">
@@ -35859,7 +35864,7 @@
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>英[ˈtəʊkiəʊ] 美[ˈtoʊkioʊ]</t>
+          <t>ˈtəʊkiəʊ ˈtoʊkioʊ</t>
         </is>
       </c>
       <c r="D1184" t="inlineStr">
@@ -36459,7 +36464,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>英[ʌnˈjuːʒuəl] 美[ʌnˈjuːʒuəl]</t>
+          <t>ʌnˈjuːʒuəl</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
@@ -36639,7 +36644,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>英[ˈwɒʃɪŋtən] 美[ˈwɑːʃɪŋtən]</t>
+          <t>ˈwɒʃɪŋtən ˈwɑːʃɪŋtən</t>
         </is>
       </c>
       <c r="D1210" t="inlineStr">
@@ -36939,7 +36944,7 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>英[ˈɪndiən] 美[ˈɪndiən]</t>
+          <t>ˈɪndiən</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
@@ -38049,7 +38054,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>英[ˈæfrɪkə] 美[ˈæfrɪkə]</t>
+          <t>ˈæfrɪkə</t>
         </is>
       </c>
       <c r="D1257" t="inlineStr">
@@ -39489,7 +39494,7 @@
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>英[ʃɑːk] 美[ʃɑːrk]</t>
+          <t>ʃɑːk ʃɑːrk</t>
         </is>
       </c>
       <c r="D1305" t="inlineStr">
@@ -39969,7 +39974,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>英[ˈmɒskəʊ] 美[ˈmɑːskaʊ]</t>
+          <t>ˈmɒskəʊ ˈmɑːskaʊ</t>
         </is>
       </c>
       <c r="D1321" t="inlineStr">
@@ -39999,7 +40004,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>英[bɜːˈlɪn] 美[bɜːrˈlɪn]</t>
+          <t>bɜːˈlɪn bɜːrˈlɪn</t>
         </is>
       </c>
       <c r="D1322" t="inlineStr">
@@ -40029,7 +40034,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>英[bɑːn] 美[bɑːrn]</t>
+          <t>bɑːn bɑːrn</t>
         </is>
       </c>
       <c r="D1323" t="inlineStr">
@@ -40269,7 +40274,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>英[ˈlaɪftaɪm] 美[ˈlaɪftaɪm]</t>
+          <t>ˈlaɪftaɪm</t>
         </is>
       </c>
       <c r="D1331" t="inlineStr">
@@ -40929,7 +40934,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>英[ˈenɪtaɪm] 美[ˈeniˌtaɪm]</t>
+          <t>ˈenɪtaɪm ˈeniˌtaɪm</t>
         </is>
       </c>
       <c r="D1353" t="inlineStr">
@@ -41049,7 +41054,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>英[ˈsɪdni] 美[ˈsɪdni]</t>
+          <t>ˈsɪdni</t>
         </is>
       </c>
       <c r="D1357" t="inlineStr">
@@ -41109,7 +41114,7 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>英[tʃɪps] 美[tʃɪps]</t>
+          <t>tʃɪps</t>
         </is>
       </c>
       <c r="D1359" t="inlineStr">
@@ -41199,7 +41204,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>英[dʒəˈpæn] 美[dʒəˈpæn]</t>
+          <t>dʒəˈpæn</t>
         </is>
       </c>
       <c r="D1362" t="inlineStr">
@@ -41319,7 +41324,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>英[rəʊm] 美[roʊm]</t>
+          <t>rəʊm roʊm</t>
         </is>
       </c>
       <c r="D1366" t="inlineStr">
@@ -42069,7 +42074,7 @@
       </c>
       <c r="C1391" t="inlineStr">
         <is>
-          <t>英[dəˈrektli] 美[dəˈrektli; daɪˈrektli]</t>
+          <t>dəˈrektli dəˈrektli; daɪˈrektli</t>
         </is>
       </c>
       <c r="D1391" t="inlineStr">
@@ -42099,7 +42104,7 @@
       </c>
       <c r="C1392" t="inlineStr">
         <is>
-          <t>英[jen] 美[jen]</t>
+          <t>jen</t>
         </is>
       </c>
       <c r="D1392" t="inlineStr">
@@ -42129,7 +42134,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>英[ˈdʒɜːməni] 美[ˈdʒɜːrməni]</t>
+          <t>ˈdʒɜːməni ˈdʒɜːrməni</t>
         </is>
       </c>
       <c r="D1393" t="inlineStr">
@@ -42339,7 +42344,7 @@
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>英[dʒɪm] 美[dʒɪm]</t>
+          <t>dʒɪm</t>
         </is>
       </c>
       <c r="D1400" t="inlineStr">
@@ -42399,7 +42404,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>英[ˈbɒstən] 美[ˈbɔːstən; ˈbɑːstən]</t>
+          <t>ˈbɒstən ˈbɔːstən; ˈbɑːstən</t>
         </is>
       </c>
       <c r="D1402" t="inlineStr">
@@ -42489,7 +42494,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>英[ˈdɔːbel] 美[ˈdɔːrbel]</t>
+          <t>ˈdɔːbel ˈdɔːrbel</t>
         </is>
       </c>
       <c r="D1405" t="inlineStr">
@@ -42579,7 +42584,7 @@
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>英[ˈiː meɪl] 美[ˈiː meɪl]</t>
+          <t>ˈiː meɪl</t>
         </is>
       </c>
       <c r="D1408" t="inlineStr">
@@ -42699,7 +42704,7 @@
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>英[ˈfraɪt(ə)nd] 美[ˈfraɪt(ə)nd]</t>
+          <t>ˈfraɪt(ə)nd</t>
         </is>
       </c>
       <c r="E1412" t="inlineStr">
@@ -42934,7 +42939,7 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>英[ˈkwaɪətli] 美[ˈkwaɪətli]</t>
+          <t>ˈkwaɪətli</t>
         </is>
       </c>
       <c r="D1420" t="inlineStr">
@@ -43084,7 +43089,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>英[ˈbedruːm] 美[ˈbedruːm; ˈbedrʊm]</t>
+          <t>ˈbedruːm ˈbedruːm; ˈbedrʊm</t>
         </is>
       </c>
       <c r="D1425" t="inlineStr">
@@ -44104,7 +44109,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>英[ˌʌnˈlaɪk] 美[ˌʌnˈlaɪk]</t>
+          <t>ˌʌnˈlaɪk</t>
         </is>
       </c>
       <c r="D1459" t="inlineStr">
@@ -44194,7 +44199,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>英[ˈɪtəli] 美[ˈɪtəli]</t>
+          <t>ˈɪtəli</t>
         </is>
       </c>
       <c r="D1462" t="inlineStr">
@@ -44254,7 +44259,7 @@
       </c>
       <c r="C1464" t="inlineStr">
         <is>
-          <t>英[ɒˈstreɪliə] 美[ɔːˈstreɪliə]</t>
+          <t>ɒˈstreɪliə ɔːˈstreɪliə</t>
         </is>
       </c>
       <c r="D1464" t="inlineStr">
@@ -44734,7 +44739,7 @@
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>英[ˈkeəfəli] 美[ˈkerfəli]</t>
+          <t>ˈkeəfəli ˈkerfəli</t>
         </is>
       </c>
       <c r="D1480" t="inlineStr">
@@ -45124,7 +45129,7 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>英[pliːzd] 美[pliːzd]</t>
+          <t>pliːzd</t>
         </is>
       </c>
       <c r="D1493" t="inlineStr">
@@ -45244,7 +45249,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>英[ˈbeɪkə(r)] 美[ˈbeɪkər]</t>
+          <t>ˈbeɪkə(r) ˈbeɪkər</t>
         </is>
       </c>
       <c r="D1497" t="inlineStr">
@@ -45394,7 +45399,7 @@
       </c>
       <c r="C1502" t="inlineStr">
         <is>
-          <t>美[maʊθ tu maʊθ]</t>
+          <t>maʊθ tu maʊθ</t>
         </is>
       </c>
       <c r="D1502" t="inlineStr">
@@ -45484,7 +45489,7 @@
       </c>
       <c r="C1505" t="inlineStr">
         <is>
-          <t>英[ˈʃepəd] 美[ˈʃepərd]</t>
+          <t>ˈʃepəd ˈʃepərd</t>
         </is>
       </c>
       <c r="D1505" t="inlineStr">
@@ -45574,7 +45579,7 @@
       </c>
       <c r="C1508" t="inlineStr">
         <is>
-          <t>美[ɔːl ðə taɪm]</t>
+          <t>ɔːl ðə taɪm</t>
         </is>
       </c>
       <c r="E1508" t="inlineStr">
@@ -45709,7 +45714,7 @@
       </c>
       <c r="C1513" t="inlineStr">
         <is>
-          <t>英[ˈswiːd(ə)n] 美[ˈswiːd(ə)n]</t>
+          <t>ˈswiːd(ə)n</t>
         </is>
       </c>
       <c r="D1513" t="inlineStr">
@@ -45789,7 +45794,7 @@
       </c>
       <c r="C1516" t="inlineStr">
         <is>
-          <t>英[ˈfrædʒaɪl] 美[ˈfrædʒ(ə)l]</t>
+          <t>ˈfrædʒaɪl ˈfrædʒ(ə)l</t>
         </is>
       </c>
       <c r="D1516" t="inlineStr">
@@ -45819,7 +45824,7 @@
       </c>
       <c r="C1517" t="inlineStr">
         <is>
-          <t>英[ˈməʊdem] 美[ˈmoʊdəm]</t>
+          <t>ˈməʊdem ˈmoʊdəm</t>
         </is>
       </c>
       <c r="D1517" t="inlineStr">
@@ -45969,7 +45974,7 @@
       </c>
       <c r="C1522" t="inlineStr">
         <is>
-          <t>英[ˌlaʊdˈspiːkə(r)] 美[ˌlaʊdˈspiːkər]</t>
+          <t>ˌlaʊdˈspiːkə(r) ˌlaʊdˈspiːkər</t>
         </is>
       </c>
       <c r="D1522" t="inlineStr">
@@ -46199,7 +46204,7 @@
       </c>
       <c r="C1530" t="inlineStr">
         <is>
-          <t>英[ˈpærət] 美[ˈpærət]</t>
+          <t>ˈpærət</t>
         </is>
       </c>
       <c r="D1530" t="inlineStr">
@@ -46289,7 +46294,7 @@
       </c>
       <c r="C1533" t="inlineStr">
         <is>
-          <t>英[wæɡ] 美[wæɡ]</t>
+          <t>wæɡ</t>
         </is>
       </c>
       <c r="D1533" t="inlineStr">
@@ -46319,7 +46324,7 @@
       </c>
       <c r="C1534" t="inlineStr">
         <is>
-          <t>英[ˌmæn ˈmeɪd] 美[ˌmæn ˈmeɪd]</t>
+          <t>ˌmæn ˈmeɪd</t>
         </is>
       </c>
       <c r="D1534" t="inlineStr">
@@ -46439,7 +46444,7 @@
       </c>
       <c r="C1538" t="inlineStr">
         <is>
-          <t>英[fluː] 美[fluː]</t>
+          <t>fluː</t>
         </is>
       </c>
       <c r="D1538" t="inlineStr">
@@ -46539,7 +46544,7 @@
       </c>
       <c r="C1542" t="inlineStr">
         <is>
-          <t>美[æt ˈpreznt; æt ˈprezənt]</t>
+          <t>æt ˈpreznt; æt ˈprezənt</t>
         </is>
       </c>
       <c r="E1542" t="inlineStr">
@@ -46754,7 +46759,7 @@
       </c>
       <c r="C1550" t="inlineStr">
         <is>
-          <t>英[ˈmu:nkeɪk] 美[ˈmuːnkeɪk]</t>
+          <t>ˈmu:nkeɪk ˈmuːnkeɪk</t>
         </is>
       </c>
       <c r="D1550" t="inlineStr">
@@ -46839,7 +46844,7 @@
       </c>
       <c r="C1553" t="inlineStr">
         <is>
-          <t>美[əˈbʌv ɔːl]</t>
+          <t>əˈbʌv ɔːl</t>
         </is>
       </c>
       <c r="E1553" t="inlineStr">
@@ -46954,7 +46959,7 @@
       </c>
       <c r="C1557" t="inlineStr">
         <is>
-          <t>美[bi əˈbaʊt tu]</t>
+          <t>bi əˈbaʊt tu</t>
         </is>
       </c>
       <c r="E1557" t="inlineStr">
@@ -47009,7 +47014,7 @@
       </c>
       <c r="C1559" t="inlineStr">
         <is>
-          <t>英[ˈbraɪtli] 美[ˈbraɪtli]</t>
+          <t>ˈbraɪtli</t>
         </is>
       </c>
       <c r="D1559" t="inlineStr">
@@ -47039,7 +47044,7 @@
       </c>
       <c r="C1560" t="inlineStr">
         <is>
-          <t>英[ˈdʌmplɪŋ] 美[ˈdʌmplɪŋ]</t>
+          <t>ˈdʌmplɪŋ</t>
         </is>
       </c>
       <c r="D1560" t="inlineStr">
@@ -47069,7 +47074,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>英[ˈfrentʃmən] 美[ˈfrentʃmən]</t>
+          <t>ˈfrentʃmən</t>
         </is>
       </c>
       <c r="D1561" t="inlineStr">
@@ -47239,7 +47244,7 @@
       </c>
       <c r="C1567" t="inlineStr">
         <is>
-          <t>美[æt læst]</t>
+          <t>æt læst</t>
         </is>
       </c>
       <c r="E1567" t="inlineStr">
@@ -47324,7 +47329,7 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>英[ˈlʌkɪli] 美[ˈlʌkɪli]</t>
+          <t>ˈlʌkɪli</t>
         </is>
       </c>
       <c r="D1570" t="inlineStr">
@@ -47354,7 +47359,7 @@
       </c>
       <c r="C1571" t="inlineStr">
         <is>
-          <t>英[ˈʃaʊəri] 美[ˈʃaʊəri]</t>
+          <t>ˈʃaʊəri</t>
         </is>
       </c>
       <c r="D1571" t="inlineStr">
@@ -47384,7 +47389,7 @@
       </c>
       <c r="C1572" t="inlineStr">
         <is>
-          <t>英[ˈwɜːkpleɪs] 美[ˈwɜːrkpleɪs]</t>
+          <t>ˈwɜːkpleɪs ˈwɜːrkpleɪs</t>
         </is>
       </c>
       <c r="D1572" t="inlineStr">
@@ -47534,7 +47539,7 @@
       </c>
       <c r="C1577" t="inlineStr">
         <is>
-          <t>英[rɪdʒ] 美[rɪdʒ]</t>
+          <t>rɪdʒ</t>
         </is>
       </c>
       <c r="D1577" t="inlineStr">
@@ -47589,7 +47594,7 @@
       </c>
       <c r="C1579" t="inlineStr">
         <is>
-          <t>英[æz wel] 美[æz wel]</t>
+          <t>æz wel</t>
         </is>
       </c>
       <c r="E1579" t="inlineStr">
@@ -47614,7 +47619,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>英[ˈhændbæɡ] 美[ˈhændbæɡ]</t>
+          <t>ˈhændbæɡ</t>
         </is>
       </c>
       <c r="D1580" t="inlineStr">
@@ -47704,7 +47709,7 @@
       </c>
       <c r="C1583" t="inlineStr">
         <is>
-          <t>英[frʌˈstreɪtɪd] 美[ˈfrʌstreɪtɪd]</t>
+          <t>frʌˈstreɪtɪd ˈfrʌstreɪtɪd</t>
         </is>
       </c>
       <c r="E1583" t="inlineStr">
@@ -47729,7 +47734,7 @@
       </c>
       <c r="C1584" t="inlineStr">
         <is>
-          <t>英[dʒəˈrɑːf] 美[dʒəˈræf]</t>
+          <t>dʒəˈrɑːf dʒəˈræf</t>
         </is>
       </c>
       <c r="D1584" t="inlineStr">
@@ -47819,7 +47824,7 @@
       </c>
       <c r="C1587" t="inlineStr">
         <is>
-          <t>英[ˌjuː ˈkeɪ] 美[ˌjuː ˈkeɪ]</t>
+          <t>ˌjuː ˈkeɪ</t>
         </is>
       </c>
       <c r="D1587" t="inlineStr">
@@ -47849,7 +47854,7 @@
       </c>
       <c r="C1588" t="inlineStr">
         <is>
-          <t>英[ˈstraɪkə(r)] 美[ˈstraɪkər]</t>
+          <t>ˈstraɪkə(r) ˈstraɪkər</t>
         </is>
       </c>
       <c r="D1588" t="inlineStr">
@@ -47909,7 +47914,7 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>英[ˈpleɪhaʊs] 美[ˈpleɪhaʊs]</t>
+          <t>ˈpleɪhaʊs</t>
         </is>
       </c>
       <c r="D1590" t="inlineStr">
@@ -48339,7 +48344,7 @@
       </c>
       <c r="C1605" t="inlineStr">
         <is>
-          <t>美[æt liːst]</t>
+          <t>æt liːst</t>
         </is>
       </c>
       <c r="E1605" t="inlineStr">
@@ -48594,7 +48599,7 @@
       </c>
       <c r="C1614" t="inlineStr">
         <is>
-          <t>英[ˈmɪnibʌs] 美[ˈmɪnibʌs]</t>
+          <t>ˈmɪnibʌs</t>
         </is>
       </c>
       <c r="D1614" t="inlineStr">
@@ -48799,7 +48804,7 @@
       </c>
       <c r="C1621" t="inlineStr">
         <is>
-          <t>英[ˌdɪsəˈpɪərəns] 美[ˌdɪsəˈpɪrəns]</t>
+          <t>ˌdɪsəˈpɪərəns ˌdɪsəˈpɪrəns</t>
         </is>
       </c>
       <c r="D1621" t="inlineStr">
@@ -48829,7 +48834,7 @@
       </c>
       <c r="C1622" t="inlineStr">
         <is>
-          <t>英[haɪk] 美[haɪk]</t>
+          <t>haɪk</t>
         </is>
       </c>
       <c r="D1622" t="inlineStr">
@@ -48949,7 +48954,7 @@
       </c>
       <c r="C1626" t="inlineStr">
         <is>
-          <t>英[ˈtraɪaʊt] 美[ˈtraɪaʊt]</t>
+          <t>ˈtraɪaʊt</t>
         </is>
       </c>
       <c r="D1626" t="inlineStr">
@@ -49089,7 +49094,7 @@
       </c>
       <c r="C1631" t="inlineStr">
         <is>
-          <t>英[ˈhjuːmərəs] 美[ˈhjuːmərəs]</t>
+          <t>ˈhjuːmərəs</t>
         </is>
       </c>
       <c r="D1631" t="inlineStr">
@@ -49149,7 +49154,7 @@
       </c>
       <c r="C1633" t="inlineStr">
         <is>
-          <t>英[ˈrækɪt] 美[ˈrækɪt]</t>
+          <t>ˈrækɪt</t>
         </is>
       </c>
       <c r="D1633" t="inlineStr">
@@ -49179,7 +49184,7 @@
       </c>
       <c r="C1634" t="inlineStr">
         <is>
-          <t>英[ɪnˈdʒekʃ(ə)n] 美[ɪnˈdʒekʃ(ə)n]</t>
+          <t>ɪnˈdʒekʃ(ə)n</t>
         </is>
       </c>
       <c r="D1634" t="inlineStr">
@@ -49269,7 +49274,7 @@
       </c>
       <c r="C1637" t="inlineStr">
         <is>
-          <t>英[kəˈnuː] 美[kəˈnuː]</t>
+          <t>kəˈnuː</t>
         </is>
       </c>
       <c r="D1637" t="inlineStr">
@@ -49339,7 +49344,7 @@
       </c>
       <c r="C1640" t="inlineStr">
         <is>
-          <t>英[ˈkliːnə(r)] 美[ˈkliːnər]</t>
+          <t>ˈkliːnə(r) ˈkliːnər</t>
         </is>
       </c>
       <c r="D1640" t="inlineStr">
@@ -49449,7 +49454,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>英[ˈwɒʃruːm] 美[ˈwɑːʃruːm]</t>
+          <t>ˈwɒʃruːm ˈwɑːʃruːm</t>
         </is>
       </c>
       <c r="D1644" t="inlineStr">
@@ -49479,7 +49484,7 @@
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>英[ˌɔːl ˈraɪt] 美[ɔːl raɪt]</t>
+          <t>ˌɔːl ˈraɪt ɔːl raɪt</t>
         </is>
       </c>
       <c r="D1645" t="inlineStr">
@@ -49509,7 +49514,7 @@
       </c>
       <c r="C1646" t="inlineStr">
         <is>
-          <t>英[ˈslɪpə(r)] 美[ˈslɪpər]</t>
+          <t>ˈslɪpə(r) ˈslɪpər</t>
         </is>
       </c>
       <c r="D1646" t="inlineStr">
@@ -49619,7 +49624,7 @@
       </c>
       <c r="C1650" t="inlineStr">
         <is>
-          <t>英[æt wʌns] 美[æt wʌns]</t>
+          <t>æt wʌns</t>
         </is>
       </c>
       <c r="E1650" t="inlineStr">
@@ -49644,7 +49649,7 @@
       </c>
       <c r="C1651" t="inlineStr">
         <is>
-          <t>英[ˌhɑːd ˈwɜːkɪŋ] 美[ˌhɑːrd ˈwɜːrkɪŋ]</t>
+          <t>ˌhɑːd ˈwɜːkɪŋ ˌhɑːrd ˈwɜːrkɪŋ</t>
         </is>
       </c>
       <c r="D1651" t="inlineStr">
@@ -49704,7 +49709,7 @@
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>英[ˈtuːθbrʌʃ] 美[ˈtuːθbrʌʃ]</t>
+          <t>ˈtuːθbrʌʃ</t>
         </is>
       </c>
       <c r="D1653" t="inlineStr">
@@ -49734,7 +49739,7 @@
       </c>
       <c r="C1654" t="inlineStr">
         <is>
-          <t>美[əˈɡriː tu]</t>
+          <t>əˈɡriː tu</t>
         </is>
       </c>
       <c r="E1654" t="inlineStr">
@@ -49759,7 +49764,7 @@
       </c>
       <c r="C1655" t="inlineStr">
         <is>
-          <t>英[ˌeɪˈtiːnθ] 美[ˌeɪˈtiːnθ]</t>
+          <t>ˌeɪˈtiːnθ</t>
         </is>
       </c>
       <c r="D1655" t="inlineStr">
@@ -49789,7 +49794,7 @@
       </c>
       <c r="C1656" t="inlineStr">
         <is>
-          <t>美[æt ðə seɪm taɪm]</t>
+          <t>æt ðə seɪm taɪm</t>
         </is>
       </c>
       <c r="E1656" t="inlineStr">
@@ -49904,7 +49909,7 @@
       </c>
       <c r="C1660" t="inlineStr">
         <is>
-          <t>美[ɔːl ðə seɪm]</t>
+          <t>ɔːl ðə seɪm</t>
         </is>
       </c>
       <c r="E1660" t="inlineStr">
@@ -49929,7 +49934,7 @@
       </c>
       <c r="C1661" t="inlineStr">
         <is>
-          <t>英[ˌsekəndˈhænd] 美[ˌsekəndˈhænd]</t>
+          <t>ˌsekəndˈhænd</t>
         </is>
       </c>
       <c r="D1661" t="inlineStr">
@@ -50019,7 +50024,7 @@
       </c>
       <c r="C1664" t="inlineStr">
         <is>
-          <t>英[ˈpʌmpkɪn] 美[ˈpʌmpkɪn]</t>
+          <t>ˈpʌmpkɪn</t>
         </is>
       </c>
       <c r="D1664" t="inlineStr">
@@ -50109,7 +50114,7 @@
       </c>
       <c r="C1667" t="inlineStr">
         <is>
-          <t>美[æz suːn æz]</t>
+          <t>æz suːn æz</t>
         </is>
       </c>
       <c r="E1667" t="inlineStr">
@@ -50254,7 +50259,7 @@
       </c>
       <c r="C1672" t="inlineStr">
         <is>
-          <t>英[ˈɔːl deɪ] 美[ˈɔːl deɪ]</t>
+          <t>ˈɔːl deɪ</t>
         </is>
       </c>
       <c r="E1672" t="inlineStr">
@@ -50279,7 +50284,7 @@
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>英[ˌsəʊ ˈsəʊ] 美[ˌsoʊ ˈsoʊ]</t>
+          <t>ˌsəʊ ˈsəʊ ˌsoʊ ˈsoʊ</t>
         </is>
       </c>
       <c r="D1673" t="inlineStr">
@@ -50309,7 +50314,7 @@
       </c>
       <c r="C1674" t="inlineStr">
         <is>
-          <t>英[ˈdeɪtaɪm] 美[ˈdeɪtaɪm]</t>
+          <t>ˈdeɪtaɪm</t>
         </is>
       </c>
       <c r="D1674" t="inlineStr">
@@ -50624,7 +50629,7 @@
       </c>
       <c r="C1685" t="inlineStr">
         <is>
-          <t>英[ˈhəʊmtaʊn] 美[ˈhoʊmtaʊn]</t>
+          <t>ˈhəʊmtaʊn ˈhoʊmtaʊn</t>
         </is>
       </c>
       <c r="D1685" t="inlineStr">
@@ -50734,7 +50739,7 @@
       </c>
       <c r="C1689" t="inlineStr">
         <is>
-          <t>英[ˈməʊtəbaɪk] 美[ˈmoʊtərbaɪk]</t>
+          <t>ˈməʊtəbaɪk ˈmoʊtərbaɪk</t>
         </is>
       </c>
       <c r="D1689" t="inlineStr">
@@ -50794,7 +50799,7 @@
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>英[ˌwʌn ˈweɪ] 美[ˌwʌn ˈweɪ]</t>
+          <t>ˌwʌn ˈweɪ</t>
         </is>
       </c>
       <c r="D1691" t="inlineStr">
@@ -50934,7 +50939,7 @@
       </c>
       <c r="C1696" t="inlineStr">
         <is>
-          <t>英[ˈjəʊ jəʊ] 美[ˈjoʊ joʊ]</t>
+          <t>ˈjəʊ jəʊ ˈjoʊ joʊ</t>
         </is>
       </c>
       <c r="D1696" t="inlineStr">
@@ -50964,7 +50969,7 @@
       </c>
       <c r="C1697" t="inlineStr">
         <is>
-          <t>英[ˈniːtli] 美[ˈniːtli]</t>
+          <t>ˈniːtli</t>
         </is>
       </c>
       <c r="D1697" t="inlineStr">
@@ -50994,7 +50999,7 @@
       </c>
       <c r="C1698" t="inlineStr">
         <is>
-          <t>美[æt skuːl]</t>
+          <t>æt skuːl</t>
         </is>
       </c>
       <c r="E1698" t="inlineStr">
@@ -51019,7 +51024,7 @@
       </c>
       <c r="C1699" t="inlineStr">
         <is>
-          <t>英[ˈsiːfuːd] 美[ˈsiːfuːd]</t>
+          <t>ˈsiːfuːd</t>
         </is>
       </c>
       <c r="D1699" t="inlineStr">
@@ -51079,7 +51084,7 @@
       </c>
       <c r="C1701" t="inlineStr">
         <is>
-          <t>英[ˈwɔːtəmelən] 美[ˈwɔːtərmelən]</t>
+          <t>ˈwɔːtəmelən ˈwɔːtərmelən</t>
         </is>
       </c>
       <c r="D1701" t="inlineStr">
@@ -51109,7 +51114,7 @@
       </c>
       <c r="C1702" t="inlineStr">
         <is>
-          <t>英[ˈbəʊtɪŋ] 美[ˈboʊtɪŋ]</t>
+          <t>ˈbəʊtɪŋ ˈboʊtɪŋ</t>
         </is>
       </c>
       <c r="D1702" t="inlineStr">
@@ -51169,7 +51174,7 @@
       </c>
       <c r="C1704" t="inlineStr">
         <is>
-          <t>英[brəˈzɪl] 美[brəˈzɪl]</t>
+          <t>brəˈzɪl</t>
         </is>
       </c>
       <c r="D1704" t="inlineStr">
@@ -51339,7 +51344,7 @@
       </c>
       <c r="C1710" t="inlineStr">
         <is>
-          <t>美[ɔːl ɪn ɔːl]</t>
+          <t>ɔːl ɪn ɔːl</t>
         </is>
       </c>
       <c r="E1710" t="inlineStr">
@@ -51609,7 +51614,7 @@
       </c>
       <c r="C1720" t="inlineStr">
         <is>
-          <t>英[ˈtiːmwɜːk] 美[ˈtiːmwɜːrk]</t>
+          <t>ˈtiːmwɜːk ˈtiːmwɜːrk</t>
         </is>
       </c>
       <c r="D1720" t="inlineStr">
@@ -51829,7 +51834,7 @@
       </c>
       <c r="C1728" t="inlineStr">
         <is>
-          <t>英[ˌmɪdˈɔ:təm] 美[mɪd ˈɔːtəm]</t>
+          <t>ˌmɪdˈɔ:təm mɪd ˈɔːtəm</t>
         </is>
       </c>
       <c r="E1728" t="inlineStr">
@@ -52134,7 +52139,7 @@
       </c>
       <c r="C1739" t="inlineStr">
         <is>
-          <t>英[məˈkaʊ] 美[məˈkaʊ]</t>
+          <t>məˈkaʊ</t>
         </is>
       </c>
       <c r="D1739" t="inlineStr">
@@ -52194,7 +52199,7 @@
       </c>
       <c r="C1741" t="inlineStr">
         <is>
-          <t>英[ˈɪŋɡlɪʃmən] 美[ˈɪŋɡlɪʃmən]</t>
+          <t>ˈɪŋɡlɪʃmən</t>
         </is>
       </c>
       <c r="D1741" t="inlineStr">
@@ -52279,7 +52284,7 @@
       </c>
       <c r="C1744" t="inlineStr">
         <is>
-          <t>英[ˈfɒɡi] 美[ˈfɑːɡi]</t>
+          <t>ˈfɒɡi ˈfɑːɡi</t>
         </is>
       </c>
       <c r="D1744" t="inlineStr">
@@ -52309,7 +52314,7 @@
       </c>
       <c r="C1745" t="inlineStr">
         <is>
-          <t>英[krəʊ] 美[kroʊ]</t>
+          <t>krəʊ kroʊ</t>
         </is>
       </c>
       <c r="D1745" t="inlineStr">
@@ -52339,7 +52344,7 @@
       </c>
       <c r="C1746" t="inlineStr">
         <is>
-          <t>美[bi əˈweɪ frəm]</t>
+          <t>bi əˈweɪ frəm</t>
         </is>
       </c>
       <c r="E1746" t="inlineStr">
@@ -52394,7 +52399,7 @@
       </c>
       <c r="C1748" t="inlineStr">
         <is>
-          <t>英[ˈsnəʊmæn] 美[ˈsnoʊmæn]</t>
+          <t>ˈsnəʊmæn ˈsnoʊmæn</t>
         </is>
       </c>
       <c r="D1748" t="inlineStr">
@@ -52424,7 +52429,7 @@
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>英[rɪm] 美[rɪm]</t>
+          <t>rɪm</t>
         </is>
       </c>
       <c r="D1749" t="inlineStr">
@@ -52454,7 +52459,7 @@
       </c>
       <c r="C1750" t="inlineStr">
         <is>
-          <t>英[ˈskuːlbæɡ] 美[ˈskuːlˌbæɡ]</t>
+          <t>ˈskuːlbæɡ ˈskuːlˌbæɡ</t>
         </is>
       </c>
       <c r="D1750" t="inlineStr">
@@ -52484,7 +52489,7 @@
       </c>
       <c r="C1751" t="inlineStr">
         <is>
-          <t>英[skɑːf] 美[skɑːrf]</t>
+          <t>skɑːf skɑːrf</t>
         </is>
       </c>
       <c r="D1751" t="inlineStr">
@@ -52544,7 +52549,7 @@
       </c>
       <c r="C1753" t="inlineStr">
         <is>
-          <t>英[rɪˈkɔːdə(r)] 美[rɪˈkɔːrdər]</t>
+          <t>rɪˈkɔːdə(r) rɪˈkɔːrdər</t>
         </is>
       </c>
       <c r="D1753" t="inlineStr">
@@ -52574,7 +52579,7 @@
       </c>
       <c r="C1754" t="inlineStr">
         <is>
-          <t>英[ˈpɒrɪdʒ] 美[ˈpɔːrɪdʒ]</t>
+          <t>ˈpɒrɪdʒ ˈpɔːrɪdʒ</t>
         </is>
       </c>
       <c r="D1754" t="inlineStr">
@@ -52634,7 +52639,7 @@
       </c>
       <c r="C1756" t="inlineStr">
         <is>
-          <t>英[ˈbʊkmɑːk] 美[ˈbʊkmɑːrk]</t>
+          <t>ˈbʊkmɑːk ˈbʊkmɑːrk</t>
         </is>
       </c>
       <c r="D1756" t="inlineStr">
@@ -52694,7 +52699,7 @@
       </c>
       <c r="C1758" t="inlineStr">
         <is>
-          <t>英[ˈrəʊlə skeɪtɪŋ] 美[ˈroʊlər skeɪtɪŋ]</t>
+          <t>ˈrəʊlə skeɪtɪŋ ˈroʊlər skeɪtɪŋ</t>
         </is>
       </c>
       <c r="D1758" t="inlineStr">
@@ -52949,7 +52954,7 @@
       </c>
       <c r="C1767" t="inlineStr">
         <is>
-          <t>英[ˈaɪkɒn] 美[ˈaɪkɑːn]</t>
+          <t>ˈaɪkɒn ˈaɪkɑːn</t>
         </is>
       </c>
       <c r="D1767" t="inlineStr">
@@ -53029,7 +53034,7 @@
       </c>
       <c r="C1770" t="inlineStr">
         <is>
-          <t>英[ˈfɑːmlænd] 美[ˈfɑːrmlænd]</t>
+          <t>ˈfɑːmlænd ˈfɑːrmlænd</t>
         </is>
       </c>
       <c r="D1770" t="inlineStr">
@@ -53159,7 +53164,7 @@
       </c>
       <c r="C1775" t="inlineStr">
         <is>
-          <t>英[ˈwaɪdli] 美[ˈwaɪdli]</t>
+          <t>ˈwaɪdli</t>
         </is>
       </c>
       <c r="D1775" t="inlineStr">
@@ -53219,7 +53224,7 @@
       </c>
       <c r="C1777" t="inlineStr">
         <is>
-          <t>英[ˈtelɪɡrɑːf] 美[ˈtelɪɡræf]</t>
+          <t>ˈtelɪɡrɑːf ˈtelɪɡræf</t>
         </is>
       </c>
       <c r="D1777" t="inlineStr">
@@ -53359,7 +53364,7 @@
       </c>
       <c r="C1782" t="inlineStr">
         <is>
-          <t>英[ˈmuːnlaɪt] 美[ˈmuːnlaɪt]</t>
+          <t>ˈmuːnlaɪt</t>
         </is>
       </c>
       <c r="D1782" t="inlineStr">
@@ -53389,7 +53394,7 @@
       </c>
       <c r="C1783" t="inlineStr">
         <is>
-          <t>英[ˌjuː es ˈeɪ] 美[ˌjuː es ˈeɪ]</t>
+          <t>ˌjuː es ˈeɪ</t>
         </is>
       </c>
       <c r="D1783" t="inlineStr">
@@ -53419,7 +53424,7 @@
       </c>
       <c r="C1784" t="inlineStr">
         <is>
-          <t>英[ˈlaɪs(ə)ns] 美[ˈlaɪs(ə)ns]</t>
+          <t>ˈlaɪs(ə)ns</t>
         </is>
       </c>
       <c r="D1784" t="inlineStr">
@@ -53719,7 +53724,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>英[æz wel əz] 美[æz wel əz]</t>
+          <t>æz wel əz</t>
         </is>
       </c>
       <c r="E1795" t="inlineStr">
@@ -53864,7 +53869,7 @@
       </c>
       <c r="C1800" t="inlineStr">
         <is>
-          <t>英[ˈtuːθeɪk] 美[ˈtuːθeɪk]</t>
+          <t>ˈtuːθeɪk</t>
         </is>
       </c>
       <c r="D1800" t="inlineStr">
@@ -53894,7 +53899,7 @@
       </c>
       <c r="C1801" t="inlineStr">
         <is>
-          <t>英[ɪkˈsplɔːrə(r)] 美[ɪkˈsplɔːrər]</t>
+          <t>ɪkˈsplɔːrə(r) ɪkˈsplɔːrər</t>
         </is>
       </c>
       <c r="D1801" t="inlineStr">
@@ -53954,7 +53959,7 @@
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>美[ɔːl baɪ wʌnˈself]</t>
+          <t>ɔːl baɪ wʌnˈself</t>
         </is>
       </c>
       <c r="E1803" t="inlineStr">
@@ -53979,7 +53984,7 @@
       </c>
       <c r="C1804" t="inlineStr">
         <is>
-          <t>英[ˌhɑːfˈweɪ] 美[ˌhæfˈweɪ]</t>
+          <t>ˌhɑːfˈweɪ ˌhæfˈweɪ</t>
         </is>
       </c>
       <c r="D1804" t="inlineStr">
@@ -54069,7 +54074,7 @@
       </c>
       <c r="C1807" t="inlineStr">
         <is>
-          <t>英[ˌkaɪnd ˈhɑːtɪd] 美[ˌkaɪnd ˈhɑːrtɪd]</t>
+          <t>ˌkaɪnd ˈhɑːtɪd ˌkaɪnd ˈhɑːrtɪd</t>
         </is>
       </c>
       <c r="D1807" t="inlineStr">
@@ -54129,7 +54134,7 @@
       </c>
       <c r="C1809" t="inlineStr">
         <is>
-          <t>英[ˈtəʊfuː] 美[ˈtoʊfuː]</t>
+          <t>ˈtəʊfuː ˈtoʊfuː</t>
         </is>
       </c>
       <c r="D1809" t="inlineStr">
@@ -54219,7 +54224,7 @@
       </c>
       <c r="C1812" t="inlineStr">
         <is>
-          <t>英[pəˈlaɪtli] 美[pəˈlaɪtli]</t>
+          <t>pəˈlaɪtli</t>
         </is>
       </c>
       <c r="D1812" t="inlineStr">
@@ -54319,7 +54324,7 @@
       </c>
       <c r="C1816" t="inlineStr">
         <is>
-          <t>英[mæθs] 美[mæθs]</t>
+          <t>mæθs</t>
         </is>
       </c>
       <c r="D1816" t="inlineStr">
@@ -54439,7 +54444,7 @@
       </c>
       <c r="C1820" t="inlineStr">
         <is>
-          <t>美[æt ˈteɪbl]</t>
+          <t>æt ˈteɪbl</t>
         </is>
       </c>
       <c r="E1820" t="inlineStr">
@@ -54464,7 +54469,7 @@
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>英[ˈpəʊst(ə)l] 美[ˈpoʊst(ə)l]</t>
+          <t>ˈpəʊst(ə)l ˈpoʊst(ə)l</t>
         </is>
       </c>
       <c r="D1821" t="inlineStr">
@@ -54494,7 +54499,7 @@
       </c>
       <c r="C1822" t="inlineStr">
         <is>
-          <t>英[ˈmaɪkrəʊkəmpjuːtə(r)] 美[ˈmaɪkroʊkəmpjuːtər]</t>
+          <t>ˈmaɪkrəʊkəmpjuːtə(r) ˈmaɪkroʊkəmpjuːtər</t>
         </is>
       </c>
       <c r="D1822" t="inlineStr">
@@ -54524,7 +54529,7 @@
       </c>
       <c r="C1823" t="inlineStr">
         <is>
-          <t>英[ˈswiːdɪʃ] 美[ˈswiːdɪʃ]</t>
+          <t>ˈswiːdɪʃ</t>
         </is>
       </c>
       <c r="D1823" t="inlineStr">
@@ -54794,7 +54799,7 @@
       </c>
       <c r="C1832" t="inlineStr">
         <is>
-          <t>英[vet] 美[vet]</t>
+          <t>vet</t>
         </is>
       </c>
       <c r="D1832" t="inlineStr">
@@ -54824,7 +54829,7 @@
       </c>
       <c r="C1833" t="inlineStr">
         <is>
-          <t>英[səkˈsesfəli] 美[səkˈsesfəli]</t>
+          <t>səkˈsesfəli</t>
         </is>
       </c>
       <c r="D1833" t="inlineStr">
@@ -54884,7 +54889,7 @@
       </c>
       <c r="C1835" t="inlineStr">
         <is>
-          <t>英[ˈʌndəsiː] 美[ˈʌndərsiː]</t>
+          <t>ˈʌndəsiː ˈʌndərsiː</t>
         </is>
       </c>
       <c r="D1835" t="inlineStr">
@@ -54974,7 +54979,7 @@
       </c>
       <c r="C1838" t="inlineStr">
         <is>
-          <t>美[tuː ˈstɔːri]</t>
+          <t>tuː ˈstɔːri</t>
         </is>
       </c>
       <c r="E1838" t="inlineStr">
@@ -55029,7 +55034,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>英[riːf] 美[riːf]</t>
+          <t>riːf</t>
         </is>
       </c>
       <c r="D1840" t="inlineStr">
@@ -55089,7 +55094,7 @@
       </c>
       <c r="C1842" t="inlineStr">
         <is>
-          <t>英[ə fjuː] 美[ə fjuː]</t>
+          <t>ə fjuː</t>
         </is>
       </c>
       <c r="E1842" t="inlineStr">
@@ -55174,7 +55179,7 @@
       </c>
       <c r="C1845" t="inlineStr">
         <is>
-          <t>美[bi ˈeɪbl tu]</t>
+          <t>bi ˈeɪbl tu</t>
         </is>
       </c>
       <c r="E1845" t="inlineStr">
@@ -55229,7 +55234,7 @@
       </c>
       <c r="C1847" t="inlineStr">
         <is>
-          <t>英[ˈpeŋɡwɪn] 美[ˈpeŋɡwɪn]</t>
+          <t>ˈpeŋɡwɪn</t>
         </is>
       </c>
       <c r="D1847" t="inlineStr">
@@ -55429,7 +55434,7 @@
       </c>
       <c r="C1855" t="inlineStr">
         <is>
-          <t>英[ˈdaɪnəsɔː(r)] 美[ˈdaɪnəsɔːr]</t>
+          <t>ˈdaɪnəsɔː(r) ˈdaɪnəsɔːr</t>
         </is>
       </c>
       <c r="D1855" t="inlineStr">
@@ -55459,7 +55464,7 @@
       </c>
       <c r="C1856" t="inlineStr">
         <is>
-          <t>英[ˈskuːlbɔɪ] 美[ˈskuːlbɔɪ]</t>
+          <t>ˈskuːlbɔɪ</t>
         </is>
       </c>
       <c r="D1856" t="inlineStr">
@@ -55489,7 +55494,7 @@
       </c>
       <c r="C1857" t="inlineStr">
         <is>
-          <t>美[æz ˈjuːʒʊəl]</t>
+          <t>æz ˈjuːʒʊəl</t>
         </is>
       </c>
       <c r="D1857" t="inlineStr">
@@ -55579,7 +55584,7 @@
       </c>
       <c r="C1860" t="inlineStr">
         <is>
-          <t>英[ˈzebrə] 美[ˈziːbrə]</t>
+          <t>ˈzebrə ˈziːbrə</t>
         </is>
       </c>
       <c r="D1860" t="inlineStr">
@@ -55699,7 +55704,7 @@
       </c>
       <c r="C1864" t="inlineStr">
         <is>
-          <t>英[ˈselə(r)] 美[ˈselər]</t>
+          <t>ˈselə(r) ˈselər</t>
         </is>
       </c>
       <c r="D1864" t="inlineStr">
@@ -55729,7 +55734,7 @@
       </c>
       <c r="C1865" t="inlineStr">
         <is>
-          <t>美[əˈɡen ənd əˈɡen]</t>
+          <t>əˈɡen ənd əˈɡen</t>
         </is>
       </c>
       <c r="E1865" t="inlineStr">
@@ -55754,7 +55759,7 @@
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>美[əˈraɪv æt]</t>
+          <t>əˈraɪv æt</t>
         </is>
       </c>
       <c r="E1866" t="inlineStr">
@@ -55809,7 +55814,7 @@
       </c>
       <c r="C1868" t="inlineStr">
         <is>
-          <t>英[kəˈneɪdiən] 美[kəˈneɪdiən]</t>
+          <t>kəˈneɪdiən</t>
         </is>
       </c>
       <c r="D1868" t="inlineStr">
@@ -55839,7 +55844,7 @@
       </c>
       <c r="C1869" t="inlineStr">
         <is>
-          <t>英[ˈrɒbə(r)] 美[ˈrɑːbər]</t>
+          <t>ˈrɒbə(r) ˈrɑːbər</t>
         </is>
       </c>
       <c r="D1869" t="inlineStr">
@@ -55894,7 +55899,7 @@
       </c>
       <c r="C1871" t="inlineStr">
         <is>
-          <t>英[bliːt] 美[bliːt]</t>
+          <t>bliːt</t>
         </is>
       </c>
       <c r="D1871" t="inlineStr">
@@ -55924,7 +55929,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>英[kənˈdʌktə(r)] 美[kənˈdʌktər]</t>
+          <t>kənˈdʌktə(r) kənˈdʌktər</t>
         </is>
       </c>
       <c r="D1872" t="inlineStr">
@@ -55954,7 +55959,7 @@
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>英[ˈfɑːðɪst] 美[ˈfɑːrðɪst]</t>
+          <t>ˈfɑːðɪst ˈfɑːrðɪst</t>
         </is>
       </c>
       <c r="D1873" t="inlineStr">
@@ -56014,7 +56019,7 @@
       </c>
       <c r="C1875" t="inlineStr">
         <is>
-          <t>英[ˈaɪsbɜːɡ] 美[ˈaɪsbɜːrɡ]</t>
+          <t>ˈaɪsbɜːɡ ˈaɪsbɜːrɡ</t>
         </is>
       </c>
       <c r="D1875" t="inlineStr">
@@ -56074,7 +56079,7 @@
       </c>
       <c r="C1877" t="inlineStr">
         <is>
-          <t>英[ˈdʒʌmpə(r)] 美[ˈdʒʌmpər]</t>
+          <t>ˈdʒʌmpə(r) ˈdʒʌmpər</t>
         </is>
       </c>
       <c r="D1877" t="inlineStr">
@@ -56144,7 +56149,7 @@
       </c>
       <c r="C1880" t="inlineStr">
         <is>
-          <t>英[taɪˈtænɪk] 美[taɪˈtænɪk]</t>
+          <t>taɪˈtænɪk</t>
         </is>
       </c>
       <c r="D1880" t="inlineStr">
@@ -56314,7 +56319,7 @@
       </c>
       <c r="C1886" t="inlineStr">
         <is>
-          <t>英[ˈseɪlzɡɜːl] 美[ˈseɪlzɡɜːrl]</t>
+          <t>ˈseɪlzɡɜːl ˈseɪlzɡɜːrl</t>
         </is>
       </c>
       <c r="D1886" t="inlineStr">
@@ -56374,7 +56379,7 @@
       </c>
       <c r="C1888" t="inlineStr">
         <is>
-          <t>英[ˈkreɪən; ˈkreɪɒn] 美[ˈkreɪən; ˈkreɪɑːn]</t>
+          <t>ˈkreɪən; ˈkreɪɒn ˈkreɪən; ˈkreɪɑːn</t>
         </is>
       </c>
       <c r="D1888" t="inlineStr">
@@ -56404,7 +56409,7 @@
       </c>
       <c r="C1889" t="inlineStr">
         <is>
-          <t>美[æt naɪt]</t>
+          <t>æt naɪt</t>
         </is>
       </c>
       <c r="E1889" t="inlineStr">
@@ -56429,7 +56434,7 @@
       </c>
       <c r="C1890" t="inlineStr">
         <is>
-          <t>英[ˈsɜːfə(r)] 美[ˈsɜːrfər]</t>
+          <t>ˈsɜːfə(r) ˈsɜːrfər</t>
         </is>
       </c>
       <c r="D1890" t="inlineStr">
@@ -56459,7 +56464,7 @@
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>英[tuːm] 美[tuːm]</t>
+          <t>tuːm</t>
         </is>
       </c>
       <c r="D1891" t="inlineStr">
@@ -56609,7 +56614,7 @@
       </c>
       <c r="C1896" t="inlineStr">
         <is>
-          <t>英[ˈɔːl əʊvə(r)]</t>
+          <t>ˈɔːl əʊvə(r)</t>
         </is>
       </c>
       <c r="D1896" t="inlineStr">
@@ -56669,7 +56674,7 @@
       </c>
       <c r="C1898" t="inlineStr">
         <is>
-          <t>英[ʌnˈlʌki] 美[ʌnˈlʌki]</t>
+          <t>ʌnˈlʌki</t>
         </is>
       </c>
       <c r="D1898" t="inlineStr">
@@ -56699,7 +56704,7 @@
       </c>
       <c r="C1899" t="inlineStr">
         <is>
-          <t>英[ˈlaɪfbəʊt] 美[ˈlaɪfboʊt]</t>
+          <t>ˈlaɪfbəʊt ˈlaɪfboʊt</t>
         </is>
       </c>
       <c r="D1899" t="inlineStr">
@@ -56849,7 +56854,7 @@
       </c>
       <c r="C1904" t="inlineStr">
         <is>
-          <t>英[ˈwɔːdrəʊb] 美[ˈwɔːrdroʊb]</t>
+          <t>ˈwɔːdrəʊb ˈwɔːrdroʊb</t>
         </is>
       </c>
       <c r="D1904" t="inlineStr">
@@ -56989,7 +56994,7 @@
       </c>
       <c r="C1909" t="inlineStr">
         <is>
-          <t>英[ˈtiːpɒt] 美[ˈtiːpɑːt]</t>
+          <t>ˈtiːpɒt ˈtiːpɑːt</t>
         </is>
       </c>
       <c r="D1909" t="inlineStr">
@@ -57019,7 +57024,7 @@
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>美[æz ɪf]</t>
+          <t>æz ɪf</t>
         </is>
       </c>
       <c r="E1910" t="inlineStr">
@@ -57094,7 +57099,7 @@
       </c>
       <c r="C1913" t="inlineStr">
         <is>
-          <t>英[ˈtuːθpeɪst] 美[ˈtuːθpeɪst]</t>
+          <t>ˈtuːθpeɪst</t>
         </is>
       </c>
       <c r="D1913" t="inlineStr">
@@ -57334,7 +57339,7 @@
       </c>
       <c r="C1921" t="inlineStr">
         <is>
-          <t>英[ˈsædli] 美[ˈsædli]</t>
+          <t>ˈsædli</t>
         </is>
       </c>
       <c r="D1921" t="inlineStr">
@@ -57394,7 +57399,7 @@
       </c>
       <c r="C1923" t="inlineStr">
         <is>
-          <t>美[æt nuːn]</t>
+          <t>æt nuːn</t>
         </is>
       </c>
       <c r="E1923" t="inlineStr">
@@ -57419,7 +57424,7 @@
       </c>
       <c r="C1924" t="inlineStr">
         <is>
-          <t>英[təˈrɒntəʊ] 美[təˈrɑːntoʊ]</t>
+          <t>təˈrɒntəʊ təˈrɑːntoʊ</t>
         </is>
       </c>
       <c r="D1924" t="inlineStr">
@@ -57569,7 +57574,7 @@
       </c>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>英[ˈdʌstbɪn] 美[ˈdʌstbɪn]</t>
+          <t>ˈdʌstbɪn</t>
         </is>
       </c>
       <c r="D1929" t="inlineStr">
@@ -57759,7 +57764,7 @@
       </c>
       <c r="C1936" t="inlineStr">
         <is>
-          <t>英[ˈsʌnɡlɑːsɪz] 美[ˈsʌnɡlæsɪz]</t>
+          <t>ˈsʌnɡlɑːsɪz ˈsʌnɡlæsɪz</t>
         </is>
       </c>
       <c r="D1936" t="inlineStr">
@@ -57789,7 +57794,7 @@
       </c>
       <c r="C1937" t="inlineStr">
         <is>
-          <t>英[æt ˈbrekfəst] 美[æt ˈbrekfəst]</t>
+          <t>æt ˈbrekfəst</t>
         </is>
       </c>
       <c r="E1937" t="inlineStr">
@@ -57904,7 +57909,7 @@
       </c>
       <c r="C1941" t="inlineStr">
         <is>
-          <t>英[ˌpɑːt ˈtaɪm] 美[ˌpɑːrt ˈtaɪm]</t>
+          <t>ˌpɑːt ˈtaɪm ˌpɑːrt ˈtaɪm</t>
         </is>
       </c>
       <c r="D1941" t="inlineStr">
@@ -57934,7 +57939,7 @@
       </c>
       <c r="C1942" t="inlineStr">
         <is>
-          <t>美[eɪm æt]</t>
+          <t>eɪm æt</t>
         </is>
       </c>
       <c r="E1942" t="inlineStr">
@@ -58009,7 +58014,7 @@
       </c>
       <c r="C1945" t="inlineStr">
         <is>
-          <t>英[ˈstrɔːbəri] 美[ˈstrɔːberi]</t>
+          <t>ˈstrɔːbəri ˈstrɔːberi</t>
         </is>
       </c>
       <c r="D1945" t="inlineStr">
@@ -58039,7 +58044,7 @@
       </c>
       <c r="C1946" t="inlineStr">
         <is>
-          <t>英[ˈwɒtʃtaʊə(r)] 美[ˈwɑːtʃtaʊər]</t>
+          <t>ˈwɒtʃtaʊə(r) ˈwɑːtʃtaʊər</t>
         </is>
       </c>
       <c r="D1946" t="inlineStr">
@@ -58204,7 +58209,7 @@
       </c>
       <c r="C1952" t="inlineStr">
         <is>
-          <t>英[əˈklɒk] 美[əˈklɑːk]</t>
+          <t>əˈklɒk əˈklɑːk</t>
         </is>
       </c>
       <c r="D1952" t="inlineStr">
@@ -58234,7 +58239,7 @@
       </c>
       <c r="C1953" t="inlineStr">
         <is>
-          <t>英[ˈbʊkʃɒp] 美[ˈbʊkʃɑːp]</t>
+          <t>ˈbʊkʃɒp ˈbʊkʃɑːp</t>
         </is>
       </c>
       <c r="D1953" t="inlineStr">
@@ -58264,7 +58269,7 @@
       </c>
       <c r="C1954" t="inlineStr">
         <is>
-          <t>英[ˈpens(ə)l bɒks] 美[ˈpens(ə)l bɑːks]</t>
+          <t>ˈpens(ə)l bɒks ˈpens(ə)l bɑːks</t>
         </is>
       </c>
       <c r="D1954" t="inlineStr">
@@ -58324,7 +58329,7 @@
       </c>
       <c r="C1956" t="inlineStr">
         <is>
-          <t>英[ˈhelθɪli] 美[ˈhelθɪli]</t>
+          <t>ˈhelθɪli</t>
         </is>
       </c>
       <c r="D1956" t="inlineStr">
@@ -58634,7 +58639,7 @@
       </c>
       <c r="C1967" t="inlineStr">
         <is>
-          <t>英[ˈskuːljɑːd] 美[ˈskuːljɑːrd]</t>
+          <t>ˈskuːljɑːd ˈskuːljɑːrd</t>
         </is>
       </c>
       <c r="D1967" t="inlineStr">
@@ -58804,7 +58809,7 @@
       </c>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>英[ˈtiː ʃɜːt] 美[ˈtiː ʃɜːrt]</t>
+          <t>ˈtiː ʃɜːt ˈtiː ʃɜːrt</t>
         </is>
       </c>
       <c r="D1973" t="inlineStr">
@@ -58834,7 +58839,7 @@
       </c>
       <c r="C1974" t="inlineStr">
         <is>
-          <t>英[ˈɡeɪtkiːpə(r)] 美[ˈɡeɪtkiːpər]</t>
+          <t>ˈɡeɪtkiːpə(r) ˈɡeɪtkiːpər</t>
         </is>
       </c>
       <c r="D1974" t="inlineStr">
@@ -59044,7 +59049,7 @@
       </c>
       <c r="C1982" t="inlineStr">
         <is>
-          <t>美[ə ˈlɪtl]</t>
+          <t>ə ˈlɪtl</t>
         </is>
       </c>
       <c r="D1982" t="inlineStr">
@@ -59394,7 +59399,7 @@
       </c>
       <c r="C1994" t="inlineStr">
         <is>
-          <t>英[ˈbiːpə(r)] 美[ˈbiːpər]</t>
+          <t>ˈbiːpə(r) ˈbiːpər</t>
         </is>
       </c>
       <c r="D1994" t="inlineStr">
@@ -59514,7 +59519,7 @@
       </c>
       <c r="C1998" t="inlineStr">
         <is>
-          <t>美[æt lʌntʃ]</t>
+          <t>æt lʌntʃ</t>
         </is>
       </c>
       <c r="E1998" t="inlineStr">
@@ -59539,7 +59544,7 @@
       </c>
       <c r="C1999" t="inlineStr">
         <is>
-          <t>英[ˌtwenti ˈfɜːst] 美[ˌtwenti ˈfɜːrst]</t>
+          <t>ˌtwenti ˈfɜːst ˌtwenti ˈfɜːrst</t>
         </is>
       </c>
       <c r="D1999" t="inlineStr">
@@ -59599,7 +59604,7 @@
       </c>
       <c r="C2001" t="inlineStr">
         <is>
-          <t>英[ɒˈstreɪliən] 美[ɔːˈstreɪliən]</t>
+          <t>ɒˈstreɪliən ɔːˈstreɪliən</t>
         </is>
       </c>
       <c r="D2001" t="inlineStr">
@@ -59649,7 +59654,7 @@
       </c>
       <c r="C2003" t="inlineStr">
         <is>
-          <t>美[baɪ tʃæns]</t>
+          <t>baɪ tʃæns</t>
         </is>
       </c>
       <c r="E2003" t="inlineStr">
@@ -59714,7 +59719,7 @@
       </c>
       <c r="C2006" t="inlineStr">
         <is>
-          <t>美[kʌm baɪ]</t>
+          <t>kʌm baɪ</t>
         </is>
       </c>
       <c r="E2006" t="inlineStr">
@@ -59759,7 +59764,7 @@
       </c>
       <c r="C2008" t="inlineStr">
         <is>
-          <t>美[kʌm tu noʊ]</t>
+          <t>kʌm tu noʊ</t>
         </is>
       </c>
       <c r="E2008" t="inlineStr">
@@ -59784,7 +59789,7 @@
       </c>
       <c r="C2009" t="inlineStr">
         <is>
-          <t>美[kəmˈpleɪn əˈbaʊt]</t>
+          <t>kəmˈpleɪn əˈbaʊt</t>
         </is>
       </c>
       <c r="E2009" t="inlineStr">
@@ -59829,7 +59834,7 @@
       </c>
       <c r="C2011" t="inlineStr">
         <is>
-          <t>美[bɪˈliːv ɪn]</t>
+          <t>bɪˈliːv ɪn</t>
         </is>
       </c>
       <c r="E2011" t="inlineStr">
@@ -59874,7 +59879,7 @@
       </c>
       <c r="C2013" t="inlineStr">
         <is>
-          <t>美[ɪn fækt]</t>
+          <t>ɪn fækt</t>
         </is>
       </c>
       <c r="E2013" t="inlineStr">
@@ -59899,7 +59904,7 @@
       </c>
       <c r="C2014" t="inlineStr">
         <is>
-          <t>英[les ðæn] 美[les ðæn]</t>
+          <t>les ðæn</t>
         </is>
       </c>
       <c r="D2014" t="inlineStr">
@@ -59929,7 +59934,7 @@
       </c>
       <c r="C2015" t="inlineStr">
         <is>
-          <t>美[meɪk ɪt]</t>
+          <t>meɪk ɪt</t>
         </is>
       </c>
       <c r="E2015" t="inlineStr">
@@ -59994,7 +59999,7 @@
       </c>
       <c r="C2018" t="inlineStr">
         <is>
-          <t>美[kiːp əˈweɪ frəm]</t>
+          <t>kiːp əˈweɪ frəm</t>
         </is>
       </c>
       <c r="E2018" t="inlineStr">
@@ -60059,7 +60064,7 @@
       </c>
       <c r="C2021" t="inlineStr">
         <is>
-          <t>英['hʌrɪ ʌp] 美['hɜːrɪ ʌp]</t>
+          <t>'hʌrɪ ʌp 'hɜːrɪ ʌp</t>
         </is>
       </c>
       <c r="E2021" t="inlineStr">
@@ -60084,7 +60089,7 @@
       </c>
       <c r="C2022" t="inlineStr">
         <is>
-          <t>英[lɪv ɒn] 美[lɪv ɑn]</t>
+          <t>lɪv ɒn lɪv ɑn</t>
         </is>
       </c>
       <c r="E2022" t="inlineStr">
@@ -60129,7 +60134,7 @@
       </c>
       <c r="C2024" t="inlineStr">
         <is>
-          <t>美[bi strɪkt ɪn]</t>
+          <t>bi strɪkt ɪn</t>
         </is>
       </c>
       <c r="E2024" t="inlineStr">
@@ -60154,7 +60159,7 @@
       </c>
       <c r="C2025" t="inlineStr">
         <is>
-          <t>美[fiːl laɪk ˈduːɪŋ]</t>
+          <t>fiːl laɪk ˈduːɪŋ</t>
         </is>
       </c>
       <c r="E2025" t="inlineStr">
@@ -60179,7 +60184,7 @@
       </c>
       <c r="C2026" t="inlineStr">
         <is>
-          <t>美[kiːp ɪn maɪnd]</t>
+          <t>kiːp ɪn maɪnd</t>
         </is>
       </c>
       <c r="E2026" t="inlineStr">
@@ -60204,7 +60209,7 @@
       </c>
       <c r="C2027" t="inlineStr">
         <is>
-          <t>美[bi kaɪnd tu]</t>
+          <t>bi kaɪnd tu</t>
         </is>
       </c>
       <c r="E2027" t="inlineStr">
@@ -60229,7 +60234,7 @@
       </c>
       <c r="C2028" t="inlineStr">
         <is>
-          <t>美[bi meɪd frəm]</t>
+          <t>bi meɪd frəm</t>
         </is>
       </c>
       <c r="E2028" t="inlineStr">
@@ -60254,7 +60259,7 @@
       </c>
       <c r="C2029" t="inlineStr">
         <is>
-          <t>英[ˈkʌm ɒn]</t>
+          <t>ˈkʌm ɒn</t>
         </is>
       </c>
       <c r="E2029" t="inlineStr">
@@ -60299,7 +60304,7 @@
       </c>
       <c r="C2031" t="inlineStr">
         <is>
-          <t>美[lʊk əˈraʊnd]</t>
+          <t>lʊk əˈraʊnd</t>
         </is>
       </c>
       <c r="E2031" t="inlineStr">
@@ -60364,7 +60369,7 @@
       </c>
       <c r="C2034" t="inlineStr">
         <is>
-          <t>英[dʒʌst nau] 美[dʒʌst naʊ]</t>
+          <t>dʒʌst nau dʒʌst naʊ</t>
         </is>
       </c>
       <c r="E2034" t="inlineStr">
@@ -60469,7 +60474,7 @@
       </c>
       <c r="C2039" t="inlineStr">
         <is>
-          <t>英[ˌkiːp ˈfɪt] 美[ˌkiːp ˈfɪt]</t>
+          <t>ˌkiːp ˈfɪt</t>
         </is>
       </c>
       <c r="E2039" t="inlineStr">
@@ -60514,7 +60519,7 @@
       </c>
       <c r="C2041" t="inlineStr">
         <is>
-          <t>英[ˈkɔːl ʌp] 美[kɔːl ʌp]</t>
+          <t>ˈkɔːl ʌp kɔːl ʌp</t>
         </is>
       </c>
       <c r="E2041" t="inlineStr">
@@ -60539,7 +60544,7 @@
       </c>
       <c r="C2042" t="inlineStr">
         <is>
-          <t>美[kʌm ʌp wɪð]</t>
+          <t>kʌm ʌp wɪð</t>
         </is>
       </c>
       <c r="E2042" t="inlineStr">
@@ -60564,7 +60569,7 @@
       </c>
       <c r="C2043" t="inlineStr">
         <is>
-          <t>美[meɪk ə mɪˈsteɪk]</t>
+          <t>meɪk ə mɪˈsteɪk</t>
         </is>
       </c>
       <c r="E2043" t="inlineStr">
@@ -60589,7 +60594,7 @@
       </c>
       <c r="C2044" t="inlineStr">
         <is>
-          <t>英[ɡəʊ ˈfɪʃɪŋ] 美[ɡoʊ ˈfɪʃɪŋ]</t>
+          <t>ɡəʊ ˈfɪʃɪŋ ɡoʊ ˈfɪʃɪŋ</t>
         </is>
       </c>
       <c r="E2044" t="inlineStr">
@@ -60654,7 +60659,7 @@
       </c>
       <c r="C2047" t="inlineStr">
         <is>
-          <t>美[friː frəm]</t>
+          <t>friː frəm</t>
         </is>
       </c>
       <c r="E2047" t="inlineStr">
@@ -60679,7 +60684,7 @@
       </c>
       <c r="C2048" t="inlineStr">
         <is>
-          <t>英[ˌlaɪ ˈɪn] 美[ˌlaɪ ˈɪn]</t>
+          <t>ˌlaɪ ˈɪn</t>
         </is>
       </c>
       <c r="E2048" t="inlineStr">
@@ -60704,7 +60709,7 @@
       </c>
       <c r="C2049" t="inlineStr">
         <is>
-          <t>美[ɪn ðə deɪ]</t>
+          <t>ɪn ðə deɪ</t>
         </is>
       </c>
       <c r="E2049" t="inlineStr">
@@ -60729,7 +60734,7 @@
       </c>
       <c r="C2050" t="inlineStr">
         <is>
-          <t>美[kɪl ðə taɪm]</t>
+          <t>kɪl ðə taɪm</t>
         </is>
       </c>
       <c r="E2050" t="inlineStr">
@@ -60774,7 +60779,7 @@
       </c>
       <c r="C2052" t="inlineStr">
         <is>
-          <t>美[ɪn ə ˈmɪnɪt]</t>
+          <t>ɪn ə ˈmɪnɪt</t>
         </is>
       </c>
       <c r="E2052" t="inlineStr">
@@ -60799,7 +60804,7 @@
       </c>
       <c r="C2053" t="inlineStr">
         <is>
-          <t>英[ˈlet aʊt] 美[ˈlet aʊt]</t>
+          <t>ˈlet aʊt</t>
         </is>
       </c>
       <c r="E2053" t="inlineStr">
@@ -60844,7 +60849,7 @@
       </c>
       <c r="C2055" t="inlineStr">
         <is>
-          <t>美[meɪk frendz wɪð]</t>
+          <t>meɪk frendz wɪð</t>
         </is>
       </c>
       <c r="E2055" t="inlineStr">
@@ -60869,7 +60874,7 @@
       </c>
       <c r="C2056" t="inlineStr">
         <is>
-          <t>美[meɪk ə tʃɔɪs]</t>
+          <t>meɪk ə tʃɔɪs</t>
         </is>
       </c>
       <c r="E2056" t="inlineStr">
@@ -60914,7 +60919,7 @@
       </c>
       <c r="C2058" t="inlineStr">
         <is>
-          <t>英[kʌt ʌp] 美[kʌt ʌp]</t>
+          <t>kʌt ʌp</t>
         </is>
       </c>
       <c r="E2058" t="inlineStr">
@@ -60959,7 +60964,7 @@
       </c>
       <c r="C2060" t="inlineStr">
         <is>
-          <t>美[ɡet tu]</t>
+          <t>ɡet tu</t>
         </is>
       </c>
       <c r="E2060" t="inlineStr">
@@ -60984,7 +60989,7 @@
       </c>
       <c r="C2061" t="inlineStr">
         <is>
-          <t>美[duː ˈbɪznəs; duː ˈbɪznɪs]</t>
+          <t>duː ˈbɪznəs; duː ˈbɪznɪs</t>
         </is>
       </c>
       <c r="E2061" t="inlineStr">
@@ -61009,7 +61014,7 @@
       </c>
       <c r="C2062" t="inlineStr">
         <is>
-          <t>英[ˌlaɪ ˈdaʊn] 美[ˌlaɪ ˈdaʊn]</t>
+          <t>ˌlaɪ ˈdaʊn</t>
         </is>
       </c>
       <c r="E2062" t="inlineStr">
@@ -61034,7 +61039,7 @@
       </c>
       <c r="C2063" t="inlineStr">
         <is>
-          <t>美[breɪk ˈɪntu]</t>
+          <t>breɪk ˈɪntu</t>
         </is>
       </c>
       <c r="E2063" t="inlineStr">
@@ -61059,7 +61064,7 @@
       </c>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>美[breɪk daʊn]</t>
+          <t>breɪk daʊn</t>
         </is>
       </c>
       <c r="E2064" t="inlineStr">
@@ -61104,7 +61109,7 @@
       </c>
       <c r="C2066" t="inlineStr">
         <is>
-          <t>英[meɪk ʃʊə(r)] 美[meɪk ʃʊr]</t>
+          <t>meɪk ʃʊə(r) meɪk ʃʊr</t>
         </is>
       </c>
       <c r="E2066" t="inlineStr">
@@ -61169,7 +61174,7 @@
       </c>
       <c r="C2069" t="inlineStr">
         <is>
-          <t>美[kʌm frəm]</t>
+          <t>kʌm frəm</t>
         </is>
       </c>
       <c r="E2069" t="inlineStr">
@@ -61214,7 +61219,7 @@
       </c>
       <c r="C2071" t="inlineStr">
         <is>
-          <t>英[ɪn frʌnt əv] 美[ɪn frʌnt ʌv]</t>
+          <t>ɪn frʌnt əv ɪn frʌnt ʌv</t>
         </is>
       </c>
       <c r="E2071" t="inlineStr">
@@ -61239,7 +61244,7 @@
       </c>
       <c r="C2072" t="inlineStr">
         <is>
-          <t>英[ˈfɔːl ɒf]</t>
+          <t>ˈfɔːl ɒf</t>
         </is>
       </c>
       <c r="E2072" t="inlineStr">
@@ -61324,7 +61329,7 @@
       </c>
       <c r="C2076" t="inlineStr">
         <is>
-          <t>英[ˈhæv tu] 美[ˈhæv tə; ˈhæf tə]</t>
+          <t>ˈhæv tu ˈhæv tə; ˈhæf tə</t>
         </is>
       </c>
       <c r="D2076" t="inlineStr">
@@ -61394,7 +61399,7 @@
       </c>
       <c r="C2079" t="inlineStr">
         <is>
-          <t>美[ɡɪv əˈweɪ]</t>
+          <t>ɡɪv əˈweɪ</t>
         </is>
       </c>
       <c r="E2079" t="inlineStr">
@@ -61419,7 +61424,7 @@
       </c>
       <c r="C2080" t="inlineStr">
         <is>
-          <t>美[baɪ mɪˈsteɪk]</t>
+          <t>baɪ mɪˈsteɪk</t>
         </is>
       </c>
       <c r="E2080" t="inlineStr">
@@ -61564,7 +61569,7 @@
       </c>
       <c r="C2087" t="inlineStr">
         <is>
-          <t>英[haʊ mʌtʃ] 美[haʊ mʌtʃ]</t>
+          <t>haʊ mʌtʃ</t>
         </is>
       </c>
       <c r="D2087" t="inlineStr">
@@ -61659,7 +61664,7 @@
       </c>
       <c r="C2091" t="inlineStr">
         <is>
-          <t>美[ˈhæpən tu duː]</t>
+          <t>ˈhæpən tu duː</t>
         </is>
       </c>
       <c r="E2091" t="inlineStr">
@@ -61744,7 +61749,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>英[hænd ʌp] 美[hænd ʌp]</t>
+          <t>hænd ʌp</t>
         </is>
       </c>
       <c r="E2095" t="inlineStr">
@@ -61769,7 +61774,7 @@
       </c>
       <c r="C2096" t="inlineStr">
         <is>
-          <t>美[lʊk ˈɪntə]</t>
+          <t>lʊk ˈɪntə</t>
         </is>
       </c>
       <c r="E2096" t="inlineStr">
@@ -61814,7 +61819,7 @@
       </c>
       <c r="C2098" t="inlineStr">
         <is>
-          <t>英[fɔ: iɡˈzɑ:mpl] 美[fɔr ɪɡˈzæmpəl]</t>
+          <t>fɔ: iɡˈzɑ:mpl fɔr ɪɡˈzæmpəl</t>
         </is>
       </c>
       <c r="E2098" t="inlineStr">
@@ -61839,7 +61844,7 @@
       </c>
       <c r="C2099" t="inlineStr">
         <is>
-          <t>美[ˈmænɪdʒ tu duː]</t>
+          <t>ˈmænɪdʒ tu duː</t>
         </is>
       </c>
       <c r="E2099" t="inlineStr">
@@ -61884,7 +61889,7 @@
       </c>
       <c r="C2101" t="inlineStr">
         <is>
-          <t>美[brɪŋ ʌp]</t>
+          <t>brɪŋ ʌp</t>
         </is>
       </c>
       <c r="E2101" t="inlineStr">
@@ -61954,7 +61959,7 @@
       </c>
       <c r="C2104" t="inlineStr">
         <is>
-          <t>美[breɪk ˈɪntə ˈpiːsɪz]</t>
+          <t>breɪk ˈɪntə ˈpiːsɪz</t>
         </is>
       </c>
       <c r="E2104" t="inlineStr">
@@ -62024,7 +62029,7 @@
       </c>
       <c r="C2107" t="inlineStr">
         <is>
-          <t>美[fɪks ʌp]</t>
+          <t>fɪks ʌp</t>
         </is>
       </c>
       <c r="E2107" t="inlineStr">
@@ -62049,7 +62054,7 @@
       </c>
       <c r="C2108" t="inlineStr">
         <is>
-          <t>美[kʌm tu laɪf]</t>
+          <t>kʌm tu laɪf</t>
         </is>
       </c>
       <c r="E2108" t="inlineStr">
@@ -62074,7 +62079,7 @@
       </c>
       <c r="C2109" t="inlineStr">
         <is>
-          <t>英[ˈbɪld ʌp] 美[ˈbɪld ʌp]</t>
+          <t>ˈbɪld ʌp</t>
         </is>
       </c>
       <c r="E2109" t="inlineStr">
@@ -62099,7 +62104,7 @@
       </c>
       <c r="C2110" t="inlineStr">
         <is>
-          <t>美[bi ɡʊd æt]</t>
+          <t>bi ɡʊd æt</t>
         </is>
       </c>
       <c r="E2110" t="inlineStr">
@@ -62124,7 +62129,7 @@
       </c>
       <c r="C2111" t="inlineStr">
         <is>
-          <t>美[kiːp ˈhelθi]</t>
+          <t>kiːp ˈhelθi</t>
         </is>
       </c>
       <c r="E2111" t="inlineStr">
@@ -62189,7 +62194,7 @@
       </c>
       <c r="C2114" t="inlineStr">
         <is>
-          <t>美[kʌm ɪn]</t>
+          <t>kʌm ɪn</t>
         </is>
       </c>
       <c r="E2114" t="inlineStr">
@@ -62214,7 +62219,7 @@
       </c>
       <c r="C2115" t="inlineStr">
         <is>
-          <t>美[duː wɪð]</t>
+          <t>duː wɪð</t>
         </is>
       </c>
       <c r="E2115" t="inlineStr">
@@ -62239,7 +62244,7 @@
       </c>
       <c r="C2116" t="inlineStr">
         <is>
-          <t>英[ɪnˈsted əv] 美[ɪnˈsted əv]</t>
+          <t>ɪnˈsted əv</t>
         </is>
       </c>
       <c r="D2116" t="inlineStr">
@@ -62269,7 +62274,7 @@
       </c>
       <c r="C2117" t="inlineStr">
         <is>
-          <t>美[liːv ə ˈmesɪdʒ]</t>
+          <t>liːv ə ˈmesɪdʒ</t>
         </is>
       </c>
       <c r="E2117" t="inlineStr">
@@ -62354,7 +62359,7 @@
       </c>
       <c r="C2121" t="inlineStr">
         <is>
-          <t>美[ɪn noʊ taɪm]</t>
+          <t>ɪn noʊ taɪm</t>
         </is>
       </c>
       <c r="E2121" t="inlineStr">
@@ -62439,7 +62444,7 @@
       </c>
       <c r="C2125" t="inlineStr">
         <is>
-          <t>美[meɪk ə səˈdʒestʃn]</t>
+          <t>meɪk ə səˈdʒestʃn</t>
         </is>
       </c>
       <c r="E2125" t="inlineStr">
@@ -62464,7 +62469,7 @@
       </c>
       <c r="C2126" t="inlineStr">
         <is>
-          <t>美[bi ˈtæləntɪd ɪn]</t>
+          <t>bi ˈtæləntɪd ɪn</t>
         </is>
       </c>
       <c r="E2126" t="inlineStr">
@@ -62489,7 +62494,7 @@
       </c>
       <c r="C2127" t="inlineStr">
         <is>
-          <t>美[ɡet mæd æt]</t>
+          <t>ɡet mæd æt</t>
         </is>
       </c>
       <c r="E2127" t="inlineStr">
@@ -62514,7 +62519,7 @@
       </c>
       <c r="C2128" t="inlineStr">
         <is>
-          <t>美[ɪn ˈdʒenrəl]</t>
+          <t>ɪn ˈdʒenrəl</t>
         </is>
       </c>
       <c r="E2128" t="inlineStr">
@@ -62619,7 +62624,7 @@
       </c>
       <c r="C2133" t="inlineStr">
         <is>
-          <t>英[ˈdrɒp ɪn]</t>
+          <t>ˈdrɒp ɪn</t>
         </is>
       </c>
       <c r="E2133" t="inlineStr">
@@ -62664,7 +62669,7 @@
       </c>
       <c r="C2135" t="inlineStr">
         <is>
-          <t>英[ɡrəʊ ʌp] 美[ɡroʊ ʌp]</t>
+          <t>ɡrəʊ ʌp ɡroʊ ʌp</t>
         </is>
       </c>
       <c r="E2135" t="inlineStr">
@@ -62689,7 +62694,7 @@
       </c>
       <c r="C2136" t="inlineStr">
         <is>
-          <t>美[bi mæd æt]</t>
+          <t>bi mæd æt</t>
         </is>
       </c>
       <c r="E2136" t="inlineStr">
@@ -62774,7 +62779,7 @@
       </c>
       <c r="C2140" t="inlineStr">
         <is>
-          <t>美[ɡet əraɪd]</t>
+          <t>ɡet əraɪd</t>
         </is>
       </c>
       <c r="E2140" t="inlineStr">
@@ -62999,7 +63004,7 @@
       </c>
       <c r="C2151" t="inlineStr">
         <is>
-          <t>美[hæv ə ˈpɪknɪk]</t>
+          <t>hæv ə ˈpɪknɪk</t>
         </is>
       </c>
       <c r="E2151" t="inlineStr">
@@ -63024,7 +63029,7 @@
       </c>
       <c r="C2152" t="inlineStr">
         <is>
-          <t>美[tʃæt wɪð]</t>
+          <t>tʃæt wɪð</t>
         </is>
       </c>
       <c r="E2152" t="inlineStr">
@@ -63049,7 +63054,7 @@
       </c>
       <c r="C2153" t="inlineStr">
         <is>
-          <t>英[ˈmeɪkʌp] 美[ˈmeɪk ʌp]</t>
+          <t>ˈmeɪkʌp ˈmeɪk ʌp</t>
         </is>
       </c>
       <c r="E2153" t="inlineStr">
@@ -63074,7 +63079,7 @@
       </c>
       <c r="C2154" t="inlineStr">
         <is>
-          <t>美[kætʃ ʌp wɪð; kætʃ ʌp wɪθ]</t>
+          <t>kætʃ ʌp wɪð; kætʃ ʌp wɪθ</t>
         </is>
       </c>
       <c r="E2154" t="inlineStr">
@@ -63099,7 +63104,7 @@
       </c>
       <c r="C2155" t="inlineStr">
         <is>
-          <t>美[ɡɪv ʌp]</t>
+          <t>ɡɪv ʌp</t>
         </is>
       </c>
       <c r="E2155" t="inlineStr">
@@ -63184,7 +63189,7 @@
       </c>
       <c r="C2159" t="inlineStr">
         <is>
-          <t>英[ˈklɪə ʌp]</t>
+          <t>ˈklɪə ʌp</t>
         </is>
       </c>
       <c r="E2159" t="inlineStr">
@@ -63209,7 +63214,7 @@
       </c>
       <c r="C2160" t="inlineStr">
         <is>
-          <t>美[fɔːl ɪl]</t>
+          <t>fɔːl ɪl</t>
         </is>
       </c>
       <c r="E2160" t="inlineStr">
@@ -63234,7 +63239,7 @@
       </c>
       <c r="C2161" t="inlineStr">
         <is>
-          <t>美[frəm taɪm tu taɪm]</t>
+          <t>frəm taɪm tu taɪm</t>
         </is>
       </c>
       <c r="E2161" t="inlineStr">
@@ -63299,7 +63304,7 @@
       </c>
       <c r="C2164" t="inlineStr">
         <is>
-          <t>美[ɡet ˈɪntə ˈtrʌbl]</t>
+          <t>ɡet ˈɪntə ˈtrʌbl</t>
         </is>
       </c>
       <c r="E2164" t="inlineStr">
@@ -63324,7 +63329,7 @@
       </c>
       <c r="C2165" t="inlineStr">
         <is>
-          <t>美[hæv ə ˈlesn]</t>
+          <t>hæv ə ˈlesn</t>
         </is>
       </c>
       <c r="E2165" t="inlineStr">
@@ -63349,7 +63354,7 @@
       </c>
       <c r="C2166" t="inlineStr">
         <is>
-          <t>美[kiːp aʊt]</t>
+          <t>kiːp aʊt</t>
         </is>
       </c>
       <c r="E2166" t="inlineStr">
@@ -63394,7 +63399,7 @@
       </c>
       <c r="C2168" t="inlineStr">
         <is>
-          <t>美[dɪˈveləp ə fɪlm]</t>
+          <t>dɪˈveləp ə fɪlm</t>
         </is>
       </c>
       <c r="E2168" t="inlineStr">
@@ -63419,7 +63424,7 @@
       </c>
       <c r="C2169" t="inlineStr">
         <is>
-          <t>英[help wʌnˈself] 美[help wʌnˈself]</t>
+          <t>help wʌnˈself</t>
         </is>
       </c>
       <c r="E2169" t="inlineStr">
@@ -63464,7 +63469,7 @@
       </c>
       <c r="C2171" t="inlineStr">
         <is>
-          <t>美[meɪk ə fɪlm]</t>
+          <t>meɪk ə fɪlm</t>
         </is>
       </c>
       <c r="E2171" t="inlineStr">
@@ -63489,7 +63494,7 @@
       </c>
       <c r="C2172" t="inlineStr">
         <is>
-          <t>美[daɪ aʊt]</t>
+          <t>daɪ aʊt</t>
         </is>
       </c>
       <c r="E2172" t="inlineStr">
@@ -63514,7 +63519,7 @@
       </c>
       <c r="C2173" t="inlineStr">
         <is>
-          <t>美[breɪk aʊt]</t>
+          <t>breɪk aʊt</t>
         </is>
       </c>
       <c r="E2173" t="inlineStr">
@@ -63539,7 +63544,7 @@
       </c>
       <c r="C2174" t="inlineStr">
         <is>
-          <t>美[bi ˈwɪlɪŋ tu duː]</t>
+          <t>bi ˈwɪlɪŋ tu duː</t>
         </is>
       </c>
       <c r="E2174" t="inlineStr">
@@ -63564,7 +63569,7 @@
       </c>
       <c r="C2175" t="inlineStr">
         <is>
-          <t>美[dɪˈskʌs əˈbaʊt]</t>
+          <t>dɪˈskʌs əˈbaʊt</t>
         </is>
       </c>
       <c r="E2175" t="inlineStr">
@@ -63629,7 +63634,7 @@
       </c>
       <c r="C2178" t="inlineStr">
         <is>
-          <t>美[baɪ ðə taɪm]</t>
+          <t>baɪ ðə taɪm</t>
         </is>
       </c>
       <c r="E2178" t="inlineStr">
@@ -63774,7 +63779,7 @@
       </c>
       <c r="C2185" t="inlineStr">
         <is>
-          <t>美[ɪnˈdʒɔɪ wʌnˈself]</t>
+          <t>ɪnˈdʒɔɪ wʌnˈself</t>
         </is>
       </c>
       <c r="E2185" t="inlineStr">
@@ -63799,7 +63804,7 @@
       </c>
       <c r="C2186" t="inlineStr">
         <is>
-          <t>美[meɪk ə dɪˈsɪʒn]</t>
+          <t>meɪk ə dɪˈsɪʒn</t>
         </is>
       </c>
       <c r="E2186" t="inlineStr">
@@ -63844,7 +63849,7 @@
       </c>
       <c r="C2188" t="inlineStr">
         <is>
-          <t>美[hæv ə lʊk æt]</t>
+          <t>hæv ə lʊk æt</t>
         </is>
       </c>
       <c r="E2188" t="inlineStr">
@@ -63909,7 +63914,7 @@
       </c>
       <c r="C2191" t="inlineStr">
         <is>
-          <t>英[ˌfeɪs tə ˈfeɪs] 美[ˌfeɪs tə ˈfeɪs]</t>
+          <t>ˌfeɪs tə ˈfeɪs</t>
         </is>
       </c>
       <c r="E2191" t="inlineStr">
@@ -63954,7 +63959,7 @@
       </c>
       <c r="C2193" t="inlineStr">
         <is>
-          <t>美[ɡriːn hænd]</t>
+          <t>ɡriːn hænd</t>
         </is>
       </c>
       <c r="D2193" t="inlineStr">
@@ -64024,7 +64029,7 @@
       </c>
       <c r="C2196" t="inlineStr">
         <is>
-          <t>美[du wel ɪn]</t>
+          <t>du wel ɪn</t>
         </is>
       </c>
       <c r="E2196" t="inlineStr">
@@ -64069,7 +64074,7 @@
       </c>
       <c r="C2198" t="inlineStr">
         <is>
-          <t>美[meɪk aʊt]</t>
+          <t>meɪk aʊt</t>
         </is>
       </c>
       <c r="E2198" t="inlineStr">
@@ -64094,7 +64099,7 @@
       </c>
       <c r="C2199" t="inlineStr">
         <is>
-          <t>英[ˈlɪsn tʊ] 美[ˈlɪsn tu]</t>
+          <t>ˈlɪsn tʊ ˈlɪsn tu</t>
         </is>
       </c>
       <c r="E2199" t="inlineStr">
@@ -64144,7 +64149,7 @@
       </c>
       <c r="C2201" t="inlineStr">
         <is>
-          <t>英[lʊk ˈɑːftə(r)] 美[lʊk ˈæftər]</t>
+          <t>lʊk ˈɑːftə(r) lʊk ˈæftər</t>
         </is>
       </c>
       <c r="E2201" t="inlineStr">
@@ -64249,7 +64254,7 @@
       </c>
       <c r="C2206" t="inlineStr">
         <is>
-          <t>英[ˈhæŋ aʊt] 美[ˈhæŋ aʊt]</t>
+          <t>ˈhæŋ aʊt</t>
         </is>
       </c>
       <c r="E2206" t="inlineStr">
@@ -64294,7 +64299,7 @@
       </c>
       <c r="C2208" t="inlineStr">
         <is>
-          <t>美[bi fed ʌp wɪð]</t>
+          <t>bi fed ʌp wɪð</t>
         </is>
       </c>
       <c r="E2208" t="inlineStr">
@@ -64339,7 +64344,7 @@
       </c>
       <c r="C2210" t="inlineStr">
         <is>
-          <t>美[ɪn red]</t>
+          <t>ɪn red</t>
         </is>
       </c>
       <c r="E2210" t="inlineStr">
@@ -64364,7 +64369,7 @@
       </c>
       <c r="C2211" t="inlineStr">
         <is>
-          <t>美[ɪn ðɪs weɪ]</t>
+          <t>ɪn ðɪs weɪ</t>
         </is>
       </c>
       <c r="E2211" t="inlineStr">
@@ -64494,7 +64499,7 @@
       </c>
       <c r="C2217" t="inlineStr">
         <is>
-          <t>美[kiːp ə ˈdaɪəri]</t>
+          <t>kiːp ə ˈdaɪəri</t>
         </is>
       </c>
       <c r="E2217" t="inlineStr">
@@ -64519,7 +64524,7 @@
       </c>
       <c r="C2218" t="inlineStr">
         <is>
-          <t>美[ɪn ði end]</t>
+          <t>ɪn ði end</t>
         </is>
       </c>
       <c r="E2218" t="inlineStr">
@@ -64564,7 +64569,7 @@
       </c>
       <c r="C2220" t="inlineStr">
         <is>
-          <t>英[end ʌp] 美[end ʌp]</t>
+          <t>end ʌp</t>
         </is>
       </c>
       <c r="E2220" t="inlineStr">
@@ -64609,7 +64614,7 @@
       </c>
       <c r="C2222" t="inlineStr">
         <is>
-          <t>美[kiːp ˈkwaɪət]</t>
+          <t>kiːp ˈkwaɪət</t>
         </is>
       </c>
       <c r="E2222" t="inlineStr">
@@ -64634,7 +64639,7 @@
       </c>
       <c r="C2223" t="inlineStr">
         <is>
-          <t>美[ˈiːvn ɪf]</t>
+          <t>ˈiːvn ɪf</t>
         </is>
       </c>
       <c r="E2223" t="inlineStr">
@@ -64659,7 +64664,7 @@
       </c>
       <c r="C2224" t="inlineStr">
         <is>
-          <t>英[ˌkʌt ˈdaʊn] 美[ˌkʌt ˈdaʊn]</t>
+          <t>ˌkʌt ˈdaʊn</t>
         </is>
       </c>
       <c r="E2224" t="inlineStr">
@@ -64769,7 +64774,7 @@
       </c>
       <c r="C2229" t="inlineStr">
         <is>
-          <t>英[ˈlaɪn ʌp] 美[ˈlaɪn ʌp]</t>
+          <t>ˈlaɪn ʌp</t>
         </is>
       </c>
       <c r="E2229" t="inlineStr">
@@ -64794,7 +64799,7 @@
       </c>
       <c r="C2230" t="inlineStr">
         <is>
-          <t>美[bi pliːzd wɪð]</t>
+          <t>bi pliːzd wɪð</t>
         </is>
       </c>
       <c r="E2230" t="inlineStr">
@@ -64909,7 +64914,7 @@
       </c>
       <c r="C2235" t="inlineStr">
         <is>
-          <t>美[ɪn ˈɪŋɡlɪʃ]</t>
+          <t>ɪn ˈɪŋɡlɪʃ</t>
         </is>
       </c>
       <c r="E2235" t="inlineStr">
@@ -65004,7 +65009,7 @@
       </c>
       <c r="C2239" t="inlineStr">
         <is>
-          <t>美[baɪ wʌnˈself]</t>
+          <t>baɪ wʌnˈself</t>
         </is>
       </c>
       <c r="E2239" t="inlineStr">
@@ -65049,7 +65054,7 @@
       </c>
       <c r="C2241" t="inlineStr">
         <is>
-          <t>英[lʊk aʊt] 美[lʊk aʊt]</t>
+          <t>lʊk aʊt</t>
         </is>
       </c>
       <c r="E2241" t="inlineStr">
@@ -65134,7 +65139,7 @@
       </c>
       <c r="C2245" t="inlineStr">
         <is>
-          <t>美[ɪn ə laʊd vɔɪs]</t>
+          <t>ɪn ə laʊd vɔɪs</t>
         </is>
       </c>
       <c r="E2245" t="inlineStr">
@@ -65159,7 +65164,7 @@
       </c>
       <c r="C2246" t="inlineStr">
         <is>
-          <t>美[les ənd les]</t>
+          <t>les ənd les</t>
         </is>
       </c>
       <c r="E2246" t="inlineStr">
@@ -65184,7 +65189,7 @@
       </c>
       <c r="C2247" t="inlineStr">
         <is>
-          <t>美[ɡɪv ə hænd]</t>
+          <t>ɡɪv ə hænd</t>
         </is>
       </c>
       <c r="E2247" t="inlineStr">
@@ -65229,7 +65234,7 @@
       </c>
       <c r="C2249" t="inlineStr">
         <is>
-          <t>美[ɡet daʊn tu]</t>
+          <t>ɡet daʊn tu</t>
         </is>
       </c>
       <c r="E2249" t="inlineStr">
@@ -65294,7 +65299,7 @@
       </c>
       <c r="C2252" t="inlineStr">
         <is>
-          <t>美[baɪ ðə weɪ]</t>
+          <t>baɪ ðə weɪ</t>
         </is>
       </c>
       <c r="E2252" t="inlineStr">
@@ -65319,7 +65324,7 @@
       </c>
       <c r="C2253" t="inlineStr">
         <is>
-          <t>美[dʒɔɪn ɪn]</t>
+          <t>dʒɔɪn ɪn</t>
         </is>
       </c>
       <c r="E2253" t="inlineStr">
@@ -65344,7 +65349,7 @@
       </c>
       <c r="C2254" t="inlineStr">
         <is>
-          <t>美[meɪk ə ˈlɪvɪŋ]</t>
+          <t>meɪk ə ˈlɪvɪŋ</t>
         </is>
       </c>
       <c r="E2254" t="inlineStr">
@@ -65449,7 +65454,7 @@
       </c>
       <c r="C2259" t="inlineStr">
         <is>
-          <t>美[kliːn aʊt]</t>
+          <t>kliːn aʊt</t>
         </is>
       </c>
       <c r="E2259" t="inlineStr">
@@ -65474,7 +65479,7 @@
       </c>
       <c r="C2260" t="inlineStr">
         <is>
-          <t>美[kʌm tu ən end]</t>
+          <t>kʌm tu ən end</t>
         </is>
       </c>
       <c r="E2260" t="inlineStr">
@@ -65499,7 +65504,7 @@
       </c>
       <c r="C2261" t="inlineStr">
         <is>
-          <t>美[meɪk ðə bed]</t>
+          <t>meɪk ðə bed</t>
         </is>
       </c>
       <c r="E2261" t="inlineStr">
@@ -65564,7 +65569,7 @@
       </c>
       <c r="C2264" t="inlineStr">
         <is>
-          <t>美[hæv ə ɡʊd taɪm]</t>
+          <t>hæv ə ɡʊd taɪm</t>
         </is>
       </c>
       <c r="E2264" t="inlineStr">
@@ -65589,7 +65594,7 @@
       </c>
       <c r="C2265" t="inlineStr">
         <is>
-          <t>英[ˈɡet aʊt] 美[ɡet aʊt]</t>
+          <t>ˈɡet aʊt ɡet aʊt</t>
         </is>
       </c>
       <c r="E2265" t="inlineStr">
@@ -65614,7 +65619,7 @@
       </c>
       <c r="C2266" t="inlineStr">
         <is>
-          <t>美[kʌm daʊn]</t>
+          <t>kʌm daʊn</t>
         </is>
       </c>
       <c r="E2266" t="inlineStr">
@@ -65659,7 +65664,7 @@
       </c>
       <c r="C2268" t="inlineStr">
         <is>
-          <t>美[ɪn ˈpʌblɪk]</t>
+          <t>ɪn ˈpʌblɪk</t>
         </is>
       </c>
       <c r="E2268" t="inlineStr">
@@ -65684,7 +65689,7 @@
       </c>
       <c r="C2269" t="inlineStr">
         <is>
-          <t>美[bi ʌp tu]</t>
+          <t>bi ʌp tu</t>
         </is>
       </c>
       <c r="E2269" t="inlineStr">
@@ -65709,7 +65714,7 @@
       </c>
       <c r="C2270" t="inlineStr">
         <is>
-          <t>美[kiːp ˈsiːkrət]</t>
+          <t>kiːp ˈsiːkrət</t>
         </is>
       </c>
       <c r="E2270" t="inlineStr">
@@ -65734,7 +65739,7 @@
       </c>
       <c r="C2271" t="inlineStr">
         <is>
-          <t>美[bi juːzd tu duː]</t>
+          <t>bi juːzd tu duː</t>
         </is>
       </c>
       <c r="E2271" t="inlineStr">
@@ -65804,7 +65809,7 @@
       </c>
       <c r="C2274" t="inlineStr">
         <is>
-          <t>美[faɪt əˈbaʊt]</t>
+          <t>faɪt əˈbaʊt</t>
         </is>
       </c>
       <c r="E2274" t="inlineStr">
@@ -65829,7 +65834,7 @@
       </c>
       <c r="C2275" t="inlineStr">
         <is>
-          <t>美[hænd ɪn]</t>
+          <t>hænd ɪn</t>
         </is>
       </c>
       <c r="E2275" t="inlineStr">
@@ -65874,7 +65879,7 @@
       </c>
       <c r="C2277" t="inlineStr">
         <is>
-          <t>美[meɪk ˈmʌni]</t>
+          <t>meɪk ˈmʌni</t>
         </is>
       </c>
       <c r="E2277" t="inlineStr">
@@ -65899,7 +65904,7 @@
       </c>
       <c r="C2278" t="inlineStr">
         <is>
-          <t>美[ɪn ɡruːps]</t>
+          <t>ɪn ɡruːps</t>
         </is>
       </c>
       <c r="E2278" t="inlineStr">
@@ -65924,7 +65929,7 @@
       </c>
       <c r="C2279" t="inlineStr">
         <is>
-          <t>美[dʒʌst ðen]</t>
+          <t>dʒʌst ðen</t>
         </is>
       </c>
       <c r="E2279" t="inlineStr">
@@ -65949,7 +65954,7 @@
       </c>
       <c r="C2280" t="inlineStr">
         <is>
-          <t>美[kʌt ɪn laɪn]</t>
+          <t>kʌt ɪn laɪn</t>
         </is>
       </c>
       <c r="E2280" t="inlineStr">
@@ -66014,7 +66019,7 @@
       </c>
       <c r="C2283" t="inlineStr">
         <is>
-          <t>英[ˈtʃek ɪn] 美[ˈtʃek ɪn]</t>
+          <t>ˈtʃek ɪn</t>
         </is>
       </c>
       <c r="E2283" t="inlineStr">
@@ -66119,7 +66124,7 @@
       </c>
       <c r="C2288" t="inlineStr">
         <is>
-          <t>美[brɪŋ aʊt]</t>
+          <t>brɪŋ aʊt</t>
         </is>
       </c>
       <c r="E2288" t="inlineStr">
@@ -66224,7 +66229,7 @@
       </c>
       <c r="C2293" t="inlineStr">
         <is>
-          <t>美[hɪr əˈbaʊt]</t>
+          <t>hɪr əˈbaʊt</t>
         </is>
       </c>
       <c r="E2293" t="inlineStr">
@@ -66249,7 +66254,7 @@
       </c>
       <c r="C2294" t="inlineStr">
         <is>
-          <t>美[ɡet ɪn]</t>
+          <t>ɡet ɪn</t>
         </is>
       </c>
       <c r="E2294" t="inlineStr">
@@ -66354,7 +66359,7 @@
       </c>
       <c r="C2299" t="inlineStr">
         <is>
-          <t>美[bi ˈɪntrəstɪd ɪn; bi ˈɪntrestɪd ɪn]</t>
+          <t>bi ˈɪntrəstɪd ɪn; bi ˈɪntrestɪd ɪn</t>
         </is>
       </c>
       <c r="E2299" t="inlineStr">
@@ -66419,7 +66424,7 @@
       </c>
       <c r="C2302" t="inlineStr">
         <is>
-          <t>美[bi lɪŋkt tu]</t>
+          <t>bi lɪŋkt tu</t>
         </is>
       </c>
       <c r="E2302" t="inlineStr">
@@ -66444,7 +66449,7 @@
       </c>
       <c r="C2303" t="inlineStr">
         <is>
-          <t>美[hænd ɪn hænd]</t>
+          <t>hænd ɪn hænd</t>
         </is>
       </c>
       <c r="E2303" t="inlineStr">
@@ -66529,7 +66534,7 @@
       </c>
       <c r="C2307" t="inlineStr">
         <is>
-          <t>英[ˈkliːn ʌp] 美[ˈkliːn ʌp]</t>
+          <t>ˈkliːn ʌp</t>
         </is>
       </c>
       <c r="E2307" t="inlineStr">
@@ -66554,7 +66559,7 @@
       </c>
       <c r="C2308" t="inlineStr">
         <is>
-          <t>美[ɡɪv bæk]</t>
+          <t>ɡɪv bæk</t>
         </is>
       </c>
       <c r="E2308" t="inlineStr">
@@ -66579,7 +66584,7 @@
       </c>
       <c r="C2309" t="inlineStr">
         <is>
-          <t>美[ɡɪv aʊt]</t>
+          <t>ɡɪv aʊt</t>
         </is>
       </c>
       <c r="E2309" t="inlineStr">
@@ -66604,7 +66609,7 @@
       </c>
       <c r="C2310" t="inlineStr">
         <is>
-          <t>美[kəˈmjuːnɪkeɪt wɪð]</t>
+          <t>kəˈmjuːnɪkeɪt wɪð</t>
         </is>
       </c>
       <c r="E2310" t="inlineStr">
@@ -66629,7 +66634,7 @@
       </c>
       <c r="C2311" t="inlineStr">
         <is>
-          <t>美[miːn tu duː]</t>
+          <t>miːn tu duː</t>
         </is>
       </c>
       <c r="E2311" t="inlineStr">
@@ -66674,7 +66679,7 @@
       </c>
       <c r="C2313" t="inlineStr">
         <is>
-          <t>美[draɪ ʌp]</t>
+          <t>draɪ ʌp</t>
         </is>
       </c>
       <c r="E2313" t="inlineStr">
@@ -66719,7 +66724,7 @@
       </c>
       <c r="C2315" t="inlineStr">
         <is>
-          <t>美[dɪˈvaɪd ˈɪntu]</t>
+          <t>dɪˈvaɪd ˈɪntu</t>
         </is>
       </c>
       <c r="E2315" t="inlineStr">
@@ -66744,7 +66749,7 @@
       </c>
       <c r="C2316" t="inlineStr">
         <is>
-          <t>美[kʌm aʊt]</t>
+          <t>kʌm aʊt</t>
         </is>
       </c>
       <c r="E2316" t="inlineStr">
@@ -66789,7 +66794,7 @@
       </c>
       <c r="C2318" t="inlineStr">
         <is>
-          <t>美[hænd aʊt]</t>
+          <t>hænd aʊt</t>
         </is>
       </c>
       <c r="E2318" t="inlineStr">
@@ -66859,7 +66864,7 @@
       </c>
       <c r="C2321" t="inlineStr">
         <is>
-          <t>美[fɔːl ˈɪntə]</t>
+          <t>fɔːl ˈɪntə</t>
         </is>
       </c>
       <c r="E2321" t="inlineStr">
@@ -66884,7 +66889,7 @@
       </c>
       <c r="C2322" t="inlineStr">
         <is>
-          <t>美[ɪn staɪl]</t>
+          <t>ɪn staɪl</t>
         </is>
       </c>
       <c r="E2322" t="inlineStr">
@@ -66929,7 +66934,7 @@
       </c>
       <c r="C2324" t="inlineStr">
         <is>
-          <t>英[ɡet bæk] 美[ɡet bæk]</t>
+          <t>ɡet bæk</t>
         </is>
       </c>
       <c r="E2324" t="inlineStr">
@@ -66954,7 +66959,7 @@
       </c>
       <c r="C2325" t="inlineStr">
         <is>
-          <t>美[liːd tu]</t>
+          <t>liːd tu</t>
         </is>
       </c>
       <c r="E2325" t="inlineStr">
@@ -66999,7 +67004,7 @@
       </c>
       <c r="C2327" t="inlineStr">
         <is>
-          <t>美[kɔːl ðə pəˈliːs]</t>
+          <t>kɔːl ðə pəˈliːs</t>
         </is>
       </c>
       <c r="E2327" t="inlineStr">
@@ -67044,7 +67049,7 @@
       </c>
       <c r="C2329" t="inlineStr">
         <is>
-          <t>美[baɪ ðen]</t>
+          <t>baɪ ðen</t>
         </is>
       </c>
       <c r="E2329" t="inlineStr">
@@ -67109,7 +67114,7 @@
       </c>
       <c r="C2332" t="inlineStr">
         <is>
-          <t>英[ˈdʒʌmp ɒf]</t>
+          <t>ˈdʒʌmp ɒf</t>
         </is>
       </c>
       <c r="E2332" t="inlineStr">
@@ -67234,7 +67239,7 @@
       </c>
       <c r="C2338" t="inlineStr">
         <is>
-          <t>美[hæv ə ˈmiːtɪŋ]</t>
+          <t>hæv ə ˈmiːtɪŋ</t>
         </is>
       </c>
       <c r="E2338" t="inlineStr">
@@ -67279,7 +67284,7 @@
       </c>
       <c r="C2340" t="inlineStr">
         <is>
-          <t>美[bi ˈredi tu duː]</t>
+          <t>bi ˈredi tu duː</t>
         </is>
       </c>
       <c r="E2340" t="inlineStr">
@@ -67304,7 +67309,7 @@
       </c>
       <c r="C2341" t="inlineStr">
         <is>
-          <t>美[noʊ əˈbaʊt]</t>
+          <t>noʊ əˈbaʊt</t>
         </is>
       </c>
       <c r="E2341" t="inlineStr">
@@ -67389,7 +67394,7 @@
       </c>
       <c r="C2345" t="inlineStr">
         <is>
-          <t>美[tʃɪr ˈʌp]</t>
+          <t>tʃɪr ˈʌp</t>
         </is>
       </c>
       <c r="E2345" t="inlineStr">
@@ -67574,7 +67579,7 @@
       </c>
       <c r="C2354" t="inlineStr">
         <is>
-          <t>美[kiːp ɪn tʌtʃ wɪð]</t>
+          <t>kiːp ɪn tʌtʃ wɪð</t>
         </is>
       </c>
       <c r="E2354" t="inlineStr">
@@ -67619,7 +67624,7 @@
       </c>
       <c r="C2356" t="inlineStr">
         <is>
-          <t>英[ɡet ʌp] 美[ɡet ʌp]</t>
+          <t>ɡet ʌp</t>
         </is>
       </c>
       <c r="E2356" t="inlineStr">
@@ -67644,7 +67649,7 @@
       </c>
       <c r="C2357" t="inlineStr">
         <is>
-          <t>美[ɪn keɪs]</t>
+          <t>ɪn keɪs</t>
         </is>
       </c>
       <c r="E2357" t="inlineStr">
@@ -67669,7 +67674,7 @@
       </c>
       <c r="C2358" t="inlineStr">
         <is>
-          <t>美[faɪnd aʊt]</t>
+          <t>faɪnd aʊt</t>
         </is>
       </c>
       <c r="E2358" t="inlineStr">
@@ -67714,7 +67719,7 @@
       </c>
       <c r="C2360" t="inlineStr">
         <is>
-          <t>美[ɡɪv ə tɔːk]</t>
+          <t>ɡɪv ə tɔːk</t>
         </is>
       </c>
       <c r="E2360" t="inlineStr">
@@ -67819,7 +67824,7 @@
       </c>
       <c r="C2365" t="inlineStr">
         <is>
-          <t>美[ɡet əˈweɪ]</t>
+          <t>ɡet əˈweɪ</t>
         </is>
       </c>
       <c r="E2365" t="inlineStr">
@@ -67864,7 +67869,7 @@
       </c>
       <c r="C2367" t="inlineStr">
         <is>
-          <t>美[haʊ suːn]</t>
+          <t>haʊ suːn</t>
         </is>
       </c>
       <c r="E2367" t="inlineStr">
@@ -67909,7 +67914,7 @@
       </c>
       <c r="C2369" t="inlineStr">
         <is>
-          <t>美[lʊk laɪk]</t>
+          <t>lʊk laɪk</t>
         </is>
       </c>
       <c r="E2369" t="inlineStr">
@@ -67954,7 +67959,7 @@
       </c>
       <c r="C2371" t="inlineStr">
         <is>
-          <t>美[lɪv baɪ]</t>
+          <t>lɪv baɪ</t>
         </is>
       </c>
       <c r="E2371" t="inlineStr">
@@ -68039,7 +68044,7 @@
       </c>
       <c r="C2375" t="inlineStr">
         <is>
-          <t>美[meɪk ˈfeɪsɪz]</t>
+          <t>meɪk ˈfeɪsɪz</t>
         </is>
       </c>
       <c r="E2375" t="inlineStr">
@@ -68084,7 +68089,7 @@
       </c>
       <c r="C2377" t="inlineStr">
         <is>
-          <t>英[ɡəʊ ˈəʊvə(r)] 美[ɡoʊ ˈoʊvər]</t>
+          <t>ɡəʊ ˈəʊvə(r) ɡoʊ ˈoʊvər</t>
         </is>
       </c>
       <c r="E2377" t="inlineStr">
@@ -68109,7 +68114,7 @@
       </c>
       <c r="C2378" t="inlineStr">
         <is>
-          <t>美[fɔːl ɪn lʌv wɪð]</t>
+          <t>fɔːl ɪn lʌv wɪð</t>
         </is>
       </c>
       <c r="E2378" t="inlineStr">
@@ -68154,7 +68159,7 @@
       </c>
       <c r="C2380" t="inlineStr">
         <is>
-          <t>英[ˈbreɪk ʌp] 美[ˈbreɪk ʌp]</t>
+          <t>ˈbreɪk ʌp</t>
         </is>
       </c>
       <c r="E2380" t="inlineStr">
@@ -68219,7 +68224,7 @@
       </c>
       <c r="C2383" t="inlineStr">
         <is>
-          <t>美[daɪ frəm]</t>
+          <t>daɪ frəm</t>
         </is>
       </c>
       <c r="E2383" t="inlineStr">
@@ -68264,7 +68269,7 @@
       </c>
       <c r="C2385" t="inlineStr">
         <is>
-          <t>美[fɪl ɪn]</t>
+          <t>fɪl ɪn</t>
         </is>
       </c>
       <c r="E2385" t="inlineStr">
@@ -68354,7 +68359,7 @@
       </c>
       <c r="C2389" t="inlineStr">
         <is>
-          <t>英[ˈhæŋ ʌp] 美[hæŋ ʌp]</t>
+          <t>ˈhæŋ ʌp hæŋ ʌp</t>
         </is>
       </c>
       <c r="E2389" t="inlineStr">
@@ -68399,7 +68404,7 @@
       </c>
       <c r="C2391" t="inlineStr">
         <is>
-          <t>美[ɪn ə mes]</t>
+          <t>ɪn ə mes</t>
         </is>
       </c>
       <c r="E2391" t="inlineStr">
@@ -68444,7 +68449,7 @@
       </c>
       <c r="C2393" t="inlineStr">
         <is>
-          <t>美[miːt wɪð]</t>
+          <t>miːt wɪð</t>
         </is>
       </c>
       <c r="E2393" t="inlineStr">
@@ -68489,7 +68494,7 @@
       </c>
       <c r="C2395" t="inlineStr">
         <is>
-          <t>美[ɡet juːzd tu ˈduːɪŋ]</t>
+          <t>ɡet juːzd tu ˈduːɪŋ</t>
         </is>
       </c>
       <c r="E2395" t="inlineStr">
@@ -68554,7 +68559,7 @@
       </c>
       <c r="C2398" t="inlineStr">
         <is>
-          <t>美[haʊ ˈmeni]</t>
+          <t>haʊ ˈmeni</t>
         </is>
       </c>
       <c r="E2398" t="inlineStr">
@@ -68579,7 +68584,7 @@
       </c>
       <c r="C2399" t="inlineStr">
         <is>
-          <t>美[bɪˈɡɪn wɪð]</t>
+          <t>bɪˈɡɪn wɪð</t>
         </is>
       </c>
       <c r="E2399" t="inlineStr">
@@ -68624,7 +68629,7 @@
       </c>
       <c r="C2401" t="inlineStr">
         <is>
-          <t>美[bi ɪl ɪn bed]</t>
+          <t>bi ɪl ɪn bed</t>
         </is>
       </c>
       <c r="E2401" t="inlineStr">
@@ -68669,7 +68674,7 @@
       </c>
       <c r="C2403" t="inlineStr">
         <is>
-          <t>美[steɪ ˈhelθi]</t>
+          <t>steɪ ˈhelθi</t>
         </is>
       </c>
       <c r="E2403" t="inlineStr">
@@ -68694,7 +68699,7 @@
       </c>
       <c r="C2404" t="inlineStr">
         <is>
-          <t>英[ˈlʊk fɔː(r)] 美[ˈlʊk fɔːr]</t>
+          <t>ˈlʊk fɔː(r) ˈlʊk fɔːr</t>
         </is>
       </c>
       <c r="E2404" t="inlineStr">
@@ -68819,7 +68824,7 @@
       </c>
       <c r="C2410" t="inlineStr">
         <is>
-          <t>英[ˈɡet təɡeðə(r)]</t>
+          <t>ˈɡet təɡeðə(r)</t>
         </is>
       </c>
       <c r="E2410" t="inlineStr">
@@ -68844,7 +68849,7 @@
       </c>
       <c r="C2411" t="inlineStr">
         <is>
-          <t>美[lʊk æt]</t>
+          <t>lʊk æt</t>
         </is>
       </c>
       <c r="E2411" t="inlineStr">
@@ -68869,7 +68874,7 @@
       </c>
       <c r="C2412" t="inlineStr">
         <is>
-          <t>美[luːz weɪt]</t>
+          <t>luːz weɪt</t>
         </is>
       </c>
       <c r="E2412" t="inlineStr">
@@ -68979,7 +68984,7 @@
       </c>
       <c r="C2417" t="inlineStr">
         <is>
-          <t>美[kiːp ʌp wɪð]</t>
+          <t>kiːp ʌp wɪð</t>
         </is>
       </c>
       <c r="E2417" t="inlineStr">
@@ -69004,7 +69009,7 @@
       </c>
       <c r="C2418" t="inlineStr">
         <is>
-          <t>英[kʌm truː] 美[kʌm truː]</t>
+          <t>kʌm truː</t>
         </is>
       </c>
       <c r="E2418" t="inlineStr">
@@ -69069,7 +69074,7 @@
       </c>
       <c r="C2421" t="inlineStr">
         <is>
-          <t>美[ɡet ɪn ðə weɪ]</t>
+          <t>ɡet ɪn ðə weɪ</t>
         </is>
       </c>
       <c r="E2421" t="inlineStr">
@@ -69114,7 +69119,7 @@
       </c>
       <c r="C2423" t="inlineStr">
         <is>
-          <t>美[ɪn ˈseɪfti]</t>
+          <t>ɪn ˈseɪfti</t>
         </is>
       </c>
       <c r="E2423" t="inlineStr">
@@ -69179,7 +69184,7 @@
       </c>
       <c r="C2426" t="inlineStr">
         <is>
-          <t>美[kɑːm daʊn]</t>
+          <t>kɑːm daʊn</t>
         </is>
       </c>
       <c r="E2426" t="inlineStr">
@@ -69249,7 +69254,7 @@
       </c>
       <c r="C2429" t="inlineStr">
         <is>
-          <t>英[dres ʌp] 美[dres ʌp]</t>
+          <t>dres ʌp</t>
         </is>
       </c>
       <c r="E2429" t="inlineStr">
@@ -69334,7 +69339,7 @@
       </c>
       <c r="C2433" t="inlineStr">
         <is>
-          <t>英[ˈlɪv ɪn] 美[ˈlɪv ɪn]</t>
+          <t>ˈlɪv ɪn</t>
         </is>
       </c>
       <c r="E2433" t="inlineStr">
@@ -69379,7 +69384,7 @@
       </c>
       <c r="C2435" t="inlineStr">
         <is>
-          <t>英[ˈlet daʊn] 美[ˈlet daʊn]</t>
+          <t>ˈlet daʊn</t>
         </is>
       </c>
       <c r="E2435" t="inlineStr">
@@ -69524,7 +69529,7 @@
       </c>
       <c r="C2442" t="inlineStr">
         <is>
-          <t>美[diːl wɪð]</t>
+          <t>diːl wɪð</t>
         </is>
       </c>
       <c r="E2442" t="inlineStr">
@@ -69549,7 +69554,7 @@
       </c>
       <c r="C2443" t="inlineStr">
         <is>
-          <t>英[hæv fʌn] 美[hæv fʌn]</t>
+          <t>hæv fʌn</t>
         </is>
       </c>
       <c r="E2443" t="inlineStr">
@@ -69614,7 +69619,7 @@
       </c>
       <c r="C2446" t="inlineStr">
         <is>
-          <t>美[fɔːl bɪˈhaɪnd]</t>
+          <t>fɔːl bɪˈhaɪnd</t>
         </is>
       </c>
       <c r="E2446" t="inlineStr">
@@ -69659,7 +69664,7 @@
       </c>
       <c r="C2448" t="inlineStr">
         <is>
-          <t>美[klaɪm ʌp]</t>
+          <t>klaɪm ʌp</t>
         </is>
       </c>
       <c r="E2448" t="inlineStr">
@@ -69724,7 +69729,7 @@
       </c>
       <c r="C2451" t="inlineStr">
         <is>
-          <t>英[ˈɡəʊ əhed]</t>
+          <t>ˈɡəʊ əhed</t>
         </is>
       </c>
       <c r="E2451" t="inlineStr">
@@ -69789,7 +69794,7 @@
       </c>
       <c r="C2454" t="inlineStr">
         <is>
-          <t>英[hæv ə rest] 美[hæv ərest]</t>
+          <t>hæv ə rest hæv ərest</t>
         </is>
       </c>
       <c r="E2454" t="inlineStr">
@@ -69834,7 +69839,7 @@
       </c>
       <c r="C2456" t="inlineStr">
         <is>
-          <t>英[ˈkæri ɒn]</t>
+          <t>ˈkæri ɒn</t>
         </is>
       </c>
       <c r="D2456" t="inlineStr">
@@ -69864,7 +69869,7 @@
       </c>
       <c r="C2457" t="inlineStr">
         <is>
-          <t>美[bi juːzd tu ˈduːɪŋ]</t>
+          <t>bi juːzd tu ˈduːɪŋ</t>
         </is>
       </c>
       <c r="E2457" t="inlineStr">
@@ -69909,7 +69914,7 @@
       </c>
       <c r="C2459" t="inlineStr">
         <is>
-          <t>美[ˈɡrædʒuət frəm]</t>
+          <t>ˈɡrædʒuət frəm</t>
         </is>
       </c>
       <c r="E2459" t="inlineStr">
@@ -69934,7 +69939,7 @@
       </c>
       <c r="C2460" t="inlineStr">
         <is>
-          <t>美[ɪn ˈtrʌbl]</t>
+          <t>ɪn ˈtrʌbl</t>
         </is>
       </c>
       <c r="E2460" t="inlineStr">
@@ -69959,7 +69964,7 @@
       </c>
       <c r="C2461" t="inlineStr">
         <is>
-          <t>美[ɪn taɪm]</t>
+          <t>ɪn taɪm</t>
         </is>
       </c>
       <c r="E2461" t="inlineStr">
@@ -70004,7 +70009,7 @@
       </c>
       <c r="C2463" t="inlineStr">
         <is>
-          <t>美[end ʌp wɪð]</t>
+          <t>end ʌp wɪð</t>
         </is>
       </c>
       <c r="E2463" t="inlineStr">
@@ -70029,7 +70034,7 @@
       </c>
       <c r="C2464" t="inlineStr">
         <is>
-          <t>美[lʊk θruː]</t>
+          <t>lʊk θruː</t>
         </is>
       </c>
       <c r="E2464" t="inlineStr">
@@ -70199,7 +70204,7 @@
       </c>
       <c r="C2472" t="inlineStr">
         <is>
-          <t>美[ɪn əˈdɪʃn]</t>
+          <t>ɪn əˈdɪʃn</t>
         </is>
       </c>
       <c r="E2472" t="inlineStr">
@@ -70264,7 +70269,7 @@
       </c>
       <c r="C2475" t="inlineStr">
         <is>
-          <t>美[læf æt]</t>
+          <t>læf æt</t>
         </is>
       </c>
       <c r="E2475" t="inlineStr">
@@ -70289,7 +70294,7 @@
       </c>
       <c r="C2476" t="inlineStr">
         <is>
-          <t>美[iːt ʌp]</t>
+          <t>iːt ʌp</t>
         </is>
       </c>
       <c r="E2476" t="inlineStr">
@@ -70379,7 +70384,7 @@
       </c>
       <c r="C2480" t="inlineStr">
         <is>
-          <t>英[ˈkæri aʊt] 美[ˈkæri aʊt]</t>
+          <t>ˈkæri aʊt</t>
         </is>
       </c>
       <c r="E2480" t="inlineStr">
@@ -70444,7 +70449,7 @@
       </c>
       <c r="C2483" t="inlineStr">
         <is>
-          <t>美[ɪn ɔːl]</t>
+          <t>ɪn ɔːl</t>
         </is>
       </c>
       <c r="E2483" t="inlineStr">
@@ -70489,7 +70494,7 @@
       </c>
       <c r="C2485" t="inlineStr">
         <is>
-          <t>英[ˈhəʊld ʌp]</t>
+          <t>ˈhəʊld ʌp</t>
         </is>
       </c>
       <c r="E2485" t="inlineStr">
@@ -70534,7 +70539,7 @@
       </c>
       <c r="C2487" t="inlineStr">
         <is>
-          <t>美[hæv ə breɪk]</t>
+          <t>hæv ə breɪk</t>
         </is>
       </c>
       <c r="E2487" t="inlineStr">
@@ -70579,7 +70584,7 @@
       </c>
       <c r="C2489" t="inlineStr">
         <is>
-          <t>美[lend tu]</t>
+          <t>lend tu</t>
         </is>
       </c>
       <c r="E2489" t="inlineStr">
@@ -70624,7 +70629,7 @@
       </c>
       <c r="C2491" t="inlineStr">
         <is>
-          <t>美[laɪt ʌp]</t>
+          <t>laɪt ʌp</t>
         </is>
       </c>
       <c r="E2491" t="inlineStr">
@@ -70734,7 +70739,7 @@
       </c>
       <c r="C2496" t="inlineStr">
         <is>
-          <t>英[tʃek aʊt] 美[tʃek aʊt]</t>
+          <t>tʃek aʊt</t>
         </is>
       </c>
       <c r="E2496" t="inlineStr">
@@ -70759,7 +70764,7 @@
       </c>
       <c r="C2497" t="inlineStr">
         <is>
-          <t>英[ˈkʌt ɒf]</t>
+          <t>ˈkʌt ɒf</t>
         </is>
       </c>
       <c r="E2497" t="inlineStr">
@@ -70784,7 +70789,7 @@
       </c>
       <c r="C2498" t="inlineStr">
         <is>
-          <t>美[breɪk ðə ruːl]</t>
+          <t>breɪk ðə ruːl</t>
         </is>
       </c>
       <c r="E2498" t="inlineStr">
@@ -70809,7 +70814,7 @@
       </c>
       <c r="C2499" t="inlineStr">
         <is>
-          <t>英[ɡet drest] 美[ɡet drest]</t>
+          <t>ɡet drest</t>
         </is>
       </c>
       <c r="E2499" t="inlineStr">
@@ -70834,7 +70839,7 @@
       </c>
       <c r="C2500" t="inlineStr">
         <is>
-          <t>美[baɪ ˈæksɪdənt]</t>
+          <t>baɪ ˈæksɪdənt</t>
         </is>
       </c>
       <c r="E2500" t="inlineStr">
@@ -70859,7 +70864,7 @@
       </c>
       <c r="C2501" t="inlineStr">
         <is>
-          <t>美[ɡɪv ɪn]</t>
+          <t>ɡɪv ɪn</t>
         </is>
       </c>
       <c r="E2501" t="inlineStr">
@@ -70924,7 +70929,7 @@
       </c>
       <c r="C2504" t="inlineStr">
         <is>
-          <t>英[ˈsel aʊt] 美[ˈsel aʊt]</t>
+          <t>ˈsel aʊt</t>
         </is>
       </c>
       <c r="E2504" t="inlineStr">
@@ -70949,7 +70954,7 @@
       </c>
       <c r="C2505" t="inlineStr">
         <is>
-          <t>美[rɪŋ ʌp]</t>
+          <t>rɪŋ ʌp</t>
         </is>
       </c>
       <c r="E2505" t="inlineStr">
@@ -70994,7 +70999,7 @@
       </c>
       <c r="C2507" t="inlineStr">
         <is>
-          <t>美[ˈnʌθɪŋ bʌt]</t>
+          <t>ˈnʌθɪŋ bʌt</t>
         </is>
       </c>
       <c r="E2507" t="inlineStr">
@@ -71019,7 +71024,7 @@
       </c>
       <c r="C2508" t="inlineStr">
         <is>
-          <t>美[steɪ əˈweɪ frəm]</t>
+          <t>steɪ əˈweɪ frəm</t>
         </is>
       </c>
       <c r="E2508" t="inlineStr">
@@ -71064,7 +71069,7 @@
       </c>
       <c r="C2510" t="inlineStr">
         <is>
-          <t>美[teɪk ɪt ˈiːzi]</t>
+          <t>teɪk ɪt ˈiːzi</t>
         </is>
       </c>
       <c r="E2510" t="inlineStr">
@@ -71149,7 +71154,7 @@
       </c>
       <c r="C2514" t="inlineStr">
         <is>
-          <t>美[pʊt əˈweɪ]</t>
+          <t>pʊt əˈweɪ</t>
         </is>
       </c>
       <c r="E2514" t="inlineStr">
@@ -71174,7 +71179,7 @@
       </c>
       <c r="C2515" t="inlineStr">
         <is>
-          <t>美[siː ə fɪlm]</t>
+          <t>siː ə fɪlm</t>
         </is>
       </c>
       <c r="E2515" t="inlineStr">
@@ -71259,7 +71264,7 @@
       </c>
       <c r="C2519" t="inlineStr">
         <is>
-          <t>英[ˈrʌn ɒf]</t>
+          <t>ˈrʌn ɒf</t>
         </is>
       </c>
       <c r="E2519" t="inlineStr">
@@ -71304,7 +71309,7 @@
       </c>
       <c r="C2521" t="inlineStr">
         <is>
-          <t>美[traɪ aʊt]</t>
+          <t>traɪ aʊt</t>
         </is>
       </c>
       <c r="E2521" t="inlineStr">
@@ -71329,7 +71334,7 @@
       </c>
       <c r="C2522" t="inlineStr">
         <is>
-          <t>美[seɪ tu wʌnˈself]</t>
+          <t>seɪ tu wʌnˈself</t>
         </is>
       </c>
       <c r="E2522" t="inlineStr">
@@ -71374,7 +71379,7 @@
       </c>
       <c r="C2524" t="inlineStr">
         <is>
-          <t>英[ˈweɪk ˌʌp] 美[ˈweɪk ˌʌp]</t>
+          <t>ˈweɪk ˌʌp</t>
         </is>
       </c>
       <c r="E2524" t="inlineStr">
@@ -71479,7 +71484,7 @@
       </c>
       <c r="C2529" t="inlineStr">
         <is>
-          <t>美[stænd baɪ]</t>
+          <t>stænd baɪ</t>
         </is>
       </c>
       <c r="E2529" t="inlineStr">
@@ -71524,7 +71529,7 @@
       </c>
       <c r="C2531" t="inlineStr">
         <is>
-          <t>英[ˈset ʌp] 美[set ʌp]</t>
+          <t>ˈset ʌp set ʌp</t>
         </is>
       </c>
       <c r="E2531" t="inlineStr">
@@ -71609,7 +71614,7 @@
       </c>
       <c r="C2535" t="inlineStr">
         <is>
-          <t>英[tɜ:n ɒn] 美[tɜːrn ɑːn]</t>
+          <t>tɜ:n ɒn tɜːrn ɑːn</t>
         </is>
       </c>
       <c r="E2535" t="inlineStr">
@@ -71654,7 +71659,7 @@
       </c>
       <c r="C2537" t="inlineStr">
         <is>
-          <t>美[teɪk ən ɪɡˈzæm]</t>
+          <t>teɪk ən ɪɡˈzæm</t>
         </is>
       </c>
       <c r="E2537" t="inlineStr">
@@ -71679,7 +71684,7 @@
       </c>
       <c r="C2538" t="inlineStr">
         <is>
-          <t>美[tel ə ˈstɔːri]</t>
+          <t>tel ə ˈstɔːri</t>
         </is>
       </c>
       <c r="E2538" t="inlineStr">
@@ -71704,7 +71709,7 @@
       </c>
       <c r="C2539" t="inlineStr">
         <is>
-          <t>美[tu səm ɪkˈstent]</t>
+          <t>tu səm ɪkˈstent</t>
         </is>
       </c>
       <c r="E2539" t="inlineStr">
@@ -71829,7 +71834,7 @@
       </c>
       <c r="C2545" t="inlineStr">
         <is>
-          <t>美[teɪk ən ˈɪntrəst ɪn]</t>
+          <t>teɪk ən ˈɪntrəst ɪn</t>
         </is>
       </c>
       <c r="E2545" t="inlineStr">
@@ -71874,7 +71879,7 @@
       </c>
       <c r="C2547" t="inlineStr">
         <is>
-          <t>美[pʊt ʌp wɪð]</t>
+          <t>pʊt ʌp wɪð</t>
         </is>
       </c>
       <c r="E2547" t="inlineStr">
@@ -71919,7 +71924,7 @@
       </c>
       <c r="C2549" t="inlineStr">
         <is>
-          <t>英[ʃʌt ʌp] 美[ʃʌt ʌp]</t>
+          <t>ʃʌt ʌp</t>
         </is>
       </c>
       <c r="E2549" t="inlineStr">
@@ -71944,7 +71949,7 @@
       </c>
       <c r="C2550" t="inlineStr">
         <is>
-          <t>英[ˈwɒʃ.ʌp] 美[ ˈwɑːʃ.ʌp]</t>
+          <t>ˈwɒʃ.ʌp ˈwɑːʃ.ʌp</t>
         </is>
       </c>
       <c r="E2550" t="inlineStr">
@@ -72029,7 +72034,7 @@
       </c>
       <c r="C2554" t="inlineStr">
         <is>
-          <t>美[wʌn baɪ wʌn]</t>
+          <t>wʌn baɪ wʌn</t>
         </is>
       </c>
       <c r="E2554" t="inlineStr">
@@ -72094,7 +72099,7 @@
       </c>
       <c r="C2557" t="inlineStr">
         <is>
-          <t>美[step baɪ step]</t>
+          <t>step baɪ step</t>
         </is>
       </c>
       <c r="E2557" t="inlineStr">
@@ -72119,7 +72124,7 @@
       </c>
       <c r="C2558" t="inlineStr">
         <is>
-          <t>美[pʊt aʊt]</t>
+          <t>pʊt aʊt</t>
         </is>
       </c>
       <c r="E2558" t="inlineStr">
@@ -72144,7 +72149,7 @@
       </c>
       <c r="C2559" t="inlineStr">
         <is>
-          <t>英[ˈpʊt daʊn] 美[pʊt daʊn]</t>
+          <t>ˈpʊt daʊn pʊt daʊn</t>
         </is>
       </c>
       <c r="E2559" t="inlineStr">
@@ -72189,7 +72194,7 @@
       </c>
       <c r="C2561" t="inlineStr">
         <is>
-          <t>英[tɜ:n left] 美[tɝ​n lɛft]</t>
+          <t>tɜ:n left tɝ​n lɛft</t>
         </is>
       </c>
       <c r="E2561" t="inlineStr">
@@ -72214,7 +72219,7 @@
       </c>
       <c r="C2562" t="inlineStr">
         <is>
-          <t>美[teɪk pleɪs]</t>
+          <t>teɪk pleɪs</t>
         </is>
       </c>
       <c r="E2562" t="inlineStr">
@@ -72239,7 +72244,7 @@
       </c>
       <c r="C2563" t="inlineStr">
         <is>
-          <t>美[ˈnekst tu]</t>
+          <t>ˈnekst tu</t>
         </is>
       </c>
       <c r="D2563" t="inlineStr">
@@ -72309,7 +72314,7 @@
       </c>
       <c r="C2566" t="inlineStr">
         <is>
-          <t>英[ˈrʌʃ aʊə(r)]</t>
+          <t>ˈrʌʃ aʊə(r)</t>
         </is>
       </c>
       <c r="D2566" t="inlineStr">
@@ -72479,7 +72484,7 @@
       </c>
       <c r="C2574" t="inlineStr">
         <is>
-          <t>英[ˌaʊt əv ˈwɜːk]</t>
+          <t>ˌaʊt əv ˈwɜːk</t>
         </is>
       </c>
       <c r="E2574" t="inlineStr">
@@ -72569,7 +72574,7 @@
       </c>
       <c r="C2578" t="inlineStr">
         <is>
-          <t>英[tɜ:n ɒf] 美[tɜːrn ɔ:f]</t>
+          <t>tɜ:n ɒf tɜːrn ɔ:f</t>
         </is>
       </c>
       <c r="E2578" t="inlineStr">
@@ -72714,7 +72719,7 @@
       </c>
       <c r="C2585" t="inlineStr">
         <is>
-          <t>英[ˈmɪks ʌp] 美[ˈmɪks ʌp]</t>
+          <t>ˈmɪks ʌp</t>
         </is>
       </c>
       <c r="E2585" t="inlineStr">
@@ -72799,7 +72804,7 @@
       </c>
       <c r="C2589" t="inlineStr">
         <is>
-          <t>美[θriː taɪmz ə wiːk]</t>
+          <t>θriː taɪmz ə wiːk</t>
         </is>
       </c>
       <c r="E2589" t="inlineStr">
@@ -72824,7 +72829,7 @@
       </c>
       <c r="C2590" t="inlineStr">
         <is>
-          <t>英[ʌp ən daʊn] 美[ʌp ənd daʊn]</t>
+          <t>ʌp ən daʊn ʌp ənd daʊn</t>
         </is>
       </c>
       <c r="E2590" t="inlineStr">
@@ -72889,7 +72894,7 @@
       </c>
       <c r="C2593" t="inlineStr">
         <is>
-          <t>美[tɔːk əˈbaʊt]</t>
+          <t>tɔːk əˈbaʊt</t>
         </is>
       </c>
       <c r="E2593" t="inlineStr">
@@ -72914,7 +72919,7 @@
       </c>
       <c r="C2594" t="inlineStr">
         <is>
-          <t>美[pʊt ʌp]</t>
+          <t>pʊt ʌp</t>
         </is>
       </c>
       <c r="E2594" t="inlineStr">
@@ -72939,7 +72944,7 @@
       </c>
       <c r="C2595" t="inlineStr">
         <is>
-          <t>美[raɪt əˈweɪ]</t>
+          <t>raɪt əˈweɪ</t>
         </is>
       </c>
       <c r="E2595" t="inlineStr">
@@ -72984,7 +72989,7 @@
       </c>
       <c r="C2597" t="inlineStr">
         <is>
-          <t>美[teɪk ɪn]</t>
+          <t>teɪk ɪn</t>
         </is>
       </c>
       <c r="E2597" t="inlineStr">
@@ -73009,7 +73014,7 @@
       </c>
       <c r="C2598" t="inlineStr">
         <is>
-          <t>美[teɪk bæk]</t>
+          <t>teɪk bæk</t>
         </is>
       </c>
       <c r="E2598" t="inlineStr">
@@ -73079,7 +73084,7 @@
       </c>
       <c r="C2601" t="inlineStr">
         <is>
-          <t>英[ˈpʊl aʊt] 美[ˈpʊl aʊt]</t>
+          <t>ˈpʊl aʊt</t>
         </is>
       </c>
       <c r="E2601" t="inlineStr">
@@ -73169,7 +73174,7 @@
       </c>
       <c r="C2605" t="inlineStr">
         <is>
-          <t>美[triːt wɪð]</t>
+          <t>triːt wɪð</t>
         </is>
       </c>
       <c r="E2605" t="inlineStr">
@@ -73194,7 +73199,7 @@
       </c>
       <c r="C2606" t="inlineStr">
         <is>
-          <t>英[mɔː(r) ðæn] 美[mɔːr ðæn]</t>
+          <t>mɔː(r) ðæn mɔːr ðæn</t>
         </is>
       </c>
       <c r="E2606" t="inlineStr">
@@ -73219,7 +73224,7 @@
       </c>
       <c r="C2607" t="inlineStr">
         <is>
-          <t>美[weɪt ɪn laɪn]</t>
+          <t>weɪt ɪn laɪn</t>
         </is>
       </c>
       <c r="E2607" t="inlineStr">
@@ -73244,7 +73249,7 @@
       </c>
       <c r="C2608" t="inlineStr">
         <is>
-          <t>美[teɪk praɪd ɪn]</t>
+          <t>teɪk praɪd ɪn</t>
         </is>
       </c>
       <c r="E2608" t="inlineStr">
@@ -73269,7 +73274,7 @@
       </c>
       <c r="C2609" t="inlineStr">
         <is>
-          <t>英[ˈsɪt daʊn] 美[ˈsɪt daʊn]</t>
+          <t>ˈsɪt daʊn</t>
         </is>
       </c>
       <c r="E2609" t="inlineStr">
@@ -73314,7 +73319,7 @@
       </c>
       <c r="C2611" t="inlineStr">
         <is>
-          <t>英['əʊvə(r) ðeə(r)] 美[ˈəʊvər ðer]</t>
+          <t>'əʊvə(r) ðeə(r) ˈəʊvər ðer</t>
         </is>
       </c>
       <c r="E2611" t="inlineStr">
@@ -73399,7 +73404,7 @@
       </c>
       <c r="C2615" t="inlineStr">
         <is>
-          <t>美[teɪk əˈweɪ]</t>
+          <t>teɪk əˈweɪ</t>
         </is>
       </c>
       <c r="D2615" t="inlineStr">
@@ -73534,7 +73539,7 @@
       </c>
       <c r="C2621" t="inlineStr">
         <is>
-          <t>英[ˈtɜːn ʌp] 美[ˈtɜːrn ʌp]</t>
+          <t>ˈtɜːn ʌp ˈtɜːrn ʌp</t>
         </is>
       </c>
       <c r="E2621" t="inlineStr">
@@ -73599,7 +73604,7 @@
       </c>
       <c r="C2624" t="inlineStr">
         <is>
-          <t>美[θɪŋk aʊt]</t>
+          <t>θɪŋk aʊt</t>
         </is>
       </c>
       <c r="E2624" t="inlineStr">
@@ -73744,7 +73749,7 @@
       </c>
       <c r="C2631" t="inlineStr">
         <is>
-          <t>美[spiːd ʌp]</t>
+          <t>spiːd ʌp</t>
         </is>
       </c>
       <c r="E2631" t="inlineStr">
@@ -73769,7 +73774,7 @@
       </c>
       <c r="C2632" t="inlineStr">
         <is>
-          <t>美[θɪŋk əˈbaʊt]</t>
+          <t>θɪŋk əˈbaʊt</t>
         </is>
       </c>
       <c r="E2632" t="inlineStr">
@@ -73814,7 +73819,7 @@
       </c>
       <c r="C2634" t="inlineStr">
         <is>
-          <t>英[set ɒf]</t>
+          <t>set ɒf</t>
         </is>
       </c>
       <c r="E2634" t="inlineStr">
@@ -73859,7 +73864,7 @@
       </c>
       <c r="C2636" t="inlineStr">
         <is>
-          <t>英[ˈpeɪ ɒf]</t>
+          <t>ˈpeɪ ɒf</t>
         </is>
       </c>
       <c r="E2636" t="inlineStr">
@@ -73964,7 +73969,7 @@
       </c>
       <c r="C2641" t="inlineStr">
         <is>
-          <t>美[teɪk ərɪsk]</t>
+          <t>teɪk ərɪsk</t>
         </is>
       </c>
       <c r="E2641" t="inlineStr">
@@ -73989,7 +73994,7 @@
       </c>
       <c r="C2642" t="inlineStr">
         <is>
-          <t>美[saʊnd laɪk]</t>
+          <t>saʊnd laɪk</t>
         </is>
       </c>
       <c r="E2642" t="inlineStr">
@@ -74034,7 +74039,7 @@
       </c>
       <c r="C2644" t="inlineStr">
         <is>
-          <t>美[ʃeɪk hændz wɪð]</t>
+          <t>ʃeɪk hændz wɪð</t>
         </is>
       </c>
       <c r="E2644" t="inlineStr">
@@ -74059,7 +74064,7 @@
       </c>
       <c r="C2645" t="inlineStr">
         <is>
-          <t>美[wʊd laɪk tu]</t>
+          <t>wʊd laɪk tu</t>
         </is>
       </c>
       <c r="E2645" t="inlineStr">
@@ -74124,7 +74129,7 @@
       </c>
       <c r="C2648" t="inlineStr">
         <is>
-          <t>英[ˈpʊl daʊn] 美[ˈpʊl daʊn]</t>
+          <t>ˈpʊl daʊn</t>
         </is>
       </c>
       <c r="E2648" t="inlineStr">
@@ -74289,7 +74294,7 @@
       </c>
       <c r="C2656" t="inlineStr">
         <is>
-          <t>美[wʌns ɪn ə waɪl]</t>
+          <t>wʌns ɪn ə waɪl</t>
         </is>
       </c>
       <c r="E2656" t="inlineStr">
@@ -74314,7 +74319,7 @@
       </c>
       <c r="C2657" t="inlineStr">
         <is>
-          <t>美[wɪð wʌn vɔɪs]</t>
+          <t>wɪð wʌn vɔɪs</t>
         </is>
       </c>
       <c r="E2657" t="inlineStr">
@@ -74359,7 +74364,7 @@
       </c>
       <c r="C2659" t="inlineStr">
         <is>
-          <t>英[pʊt ɒn] 美[pʊt ɑːn]</t>
+          <t>pʊt ɒn pʊt ɑːn</t>
         </is>
       </c>
       <c r="E2659" t="inlineStr">
@@ -74404,7 +74409,7 @@
       </c>
       <c r="C2661" t="inlineStr">
         <is>
-          <t>美[saʊnd sliːp]</t>
+          <t>saʊnd sliːp</t>
         </is>
       </c>
       <c r="D2661" t="inlineStr">
@@ -74474,7 +74479,7 @@
       </c>
       <c r="C2664" t="inlineStr">
         <is>
-          <t>英[ˈsend ʌp] 美[ˈsend ʌp]</t>
+          <t>ˈsend ʌp</t>
         </is>
       </c>
       <c r="E2664" t="inlineStr">
@@ -74604,7 +74609,7 @@
       </c>
       <c r="C2670" t="inlineStr">
         <is>
-          <t>英[pɔɪnt tu] 美[pɔɪnt tu]</t>
+          <t>pɔɪnt tu</t>
         </is>
       </c>
       <c r="E2670" t="inlineStr">
@@ -74669,7 +74674,7 @@
       </c>
       <c r="C2673" t="inlineStr">
         <is>
-          <t>美[tuː mʌtʃ]</t>
+          <t>tuː mʌtʃ</t>
         </is>
       </c>
       <c r="E2673" t="inlineStr">
@@ -74694,7 +74699,7 @@
       </c>
       <c r="C2674" t="inlineStr">
         <is>
-          <t>美[spiːk tu]</t>
+          <t>spiːk tu</t>
         </is>
       </c>
       <c r="E2674" t="inlineStr">
@@ -74719,7 +74724,7 @@
       </c>
       <c r="C2675" t="inlineStr">
         <is>
-          <t>英[muːv tu] 美[muːv tu]</t>
+          <t>muːv tu</t>
         </is>
       </c>
       <c r="E2675" t="inlineStr">
@@ -74764,7 +74769,7 @@
       </c>
       <c r="C2677" t="inlineStr">
         <is>
-          <t>美[seɪv ʌp]</t>
+          <t>seɪv ʌp</t>
         </is>
       </c>
       <c r="E2677" t="inlineStr">
@@ -74809,7 +74814,7 @@
       </c>
       <c r="C2679" t="inlineStr">
         <is>
-          <t>美[pɪk aʊt]</t>
+          <t>pɪk aʊt</t>
         </is>
       </c>
       <c r="E2679" t="inlineStr">
@@ -74894,7 +74899,7 @@
       </c>
       <c r="C2683" t="inlineStr">
         <is>
-          <t>美[ˈpræktɪs ˈduːɪŋ]</t>
+          <t>ˈpræktɪs ˈduːɪŋ</t>
         </is>
       </c>
       <c r="E2683" t="inlineStr">
@@ -74999,7 +75004,7 @@
       </c>
       <c r="C2688" t="inlineStr">
         <is>
-          <t>美[saɪd baɪ saɪd]</t>
+          <t>saɪd baɪ saɪd</t>
         </is>
       </c>
       <c r="E2688" t="inlineStr">
@@ -75024,7 +75029,7 @@
       </c>
       <c r="C2689" t="inlineStr">
         <is>
-          <t>美[riːtʃ aʊt]</t>
+          <t>riːtʃ aʊt</t>
         </is>
       </c>
       <c r="E2689" t="inlineStr">
@@ -75134,7 +75139,7 @@
       </c>
       <c r="C2694" t="inlineStr">
         <is>
-          <t>美[pʊt ˈɪntə]</t>
+          <t>pʊt ˈɪntə</t>
         </is>
       </c>
       <c r="E2694" t="inlineStr">
@@ -75299,7 +75304,7 @@
       </c>
       <c r="C2702" t="inlineStr">
         <is>
-          <t>英[ˈtaɪ ʌp] 美[ˈtaɪ ʌp]</t>
+          <t>ˈtaɪ ʌp</t>
         </is>
       </c>
       <c r="E2702" t="inlineStr">
@@ -75324,7 +75329,7 @@
       </c>
       <c r="C2703" t="inlineStr">
         <is>
-          <t>英[ˈteɪk ʌp] 美[ˈteɪk ʌp]</t>
+          <t>ˈteɪk ʌp</t>
         </is>
       </c>
       <c r="E2703" t="inlineStr">
@@ -75349,7 +75354,7 @@
       </c>
       <c r="C2704" t="inlineStr">
         <is>
-          <t>美[tel ə laɪ]</t>
+          <t>tel ə laɪ</t>
         </is>
       </c>
       <c r="E2704" t="inlineStr">
@@ -75454,7 +75459,7 @@
       </c>
       <c r="C2709" t="inlineStr">
         <is>
-          <t>英[ˌwʌn əˈnʌðə(r)]</t>
+          <t>ˌwʌn əˈnʌðə(r)</t>
         </is>
       </c>
       <c r="D2709" t="inlineStr">
@@ -75524,7 +75529,7 @@
       </c>
       <c r="C2712" t="inlineStr">
         <is>
-          <t>美[ˈtaɪdi ʌp]</t>
+          <t>ˈtaɪdi ʌp</t>
         </is>
       </c>
       <c r="E2712" t="inlineStr">
@@ -75609,7 +75614,7 @@
       </c>
       <c r="C2716" t="inlineStr">
         <is>
-          <t>美[teɪk ˈækʃn]</t>
+          <t>teɪk ˈækʃn</t>
         </is>
       </c>
       <c r="E2716" t="inlineStr">
@@ -75674,7 +75679,7 @@
       </c>
       <c r="C2719" t="inlineStr">
         <is>
-          <t>美[səm taɪm]</t>
+          <t>səm taɪm</t>
         </is>
       </c>
       <c r="E2719" t="inlineStr">
@@ -75719,7 +75724,7 @@
       </c>
       <c r="C2721" t="inlineStr">
         <is>
-          <t>英[ˈstænd ʌp] 美[ˈstænd ʌp]</t>
+          <t>ˈstænd ʌp</t>
         </is>
       </c>
       <c r="E2721" t="inlineStr">
@@ -75764,7 +75769,7 @@
       </c>
       <c r="C2723" t="inlineStr">
         <is>
-          <t>英[ˈraɪt daʊn] 美[raɪt daʊn]</t>
+          <t>ˈraɪt daʊn raɪt daʊn</t>
         </is>
       </c>
       <c r="E2723" t="inlineStr">
@@ -75874,7 +75879,7 @@
       </c>
       <c r="C2728" t="inlineStr">
         <is>
-          <t>美[tu tel ðə truːθ]</t>
+          <t>tu tel ðə truːθ</t>
         </is>
       </c>
       <c r="E2728" t="inlineStr">
@@ -75939,7 +75944,7 @@
       </c>
       <c r="C2731" t="inlineStr">
         <is>
-          <t>英[ˌʌpsaɪd ˈdaʊn] 美[ˌʌpsaɪd ˈdaʊn]</t>
+          <t>ˌʌpsaɪd ˈdaʊn</t>
         </is>
       </c>
       <c r="D2731" t="inlineStr">
@@ -75989,7 +75994,7 @@
       </c>
       <c r="C2733" t="inlineStr">
         <is>
-          <t>美[pɔɪnt aʊt]</t>
+          <t>pɔɪnt aʊt</t>
         </is>
       </c>
       <c r="E2733" t="inlineStr">
@@ -76014,7 +76019,7 @@
       </c>
       <c r="C2734" t="inlineStr">
         <is>
-          <t>美[naʊ ənd ðen]</t>
+          <t>naʊ ənd ðen</t>
         </is>
       </c>
       <c r="E2734" t="inlineStr">
@@ -76039,7 +76044,7 @@
       </c>
       <c r="C2735" t="inlineStr">
         <is>
-          <t>美[raɪt naʊ]</t>
+          <t>raɪt naʊ</t>
         </is>
       </c>
       <c r="E2735" t="inlineStr">
@@ -76064,7 +76069,7 @@
       </c>
       <c r="C2736" t="inlineStr">
         <is>
-          <t>英[kwaɪt ə fjuː] 美[kwaɪt ə fjuː]</t>
+          <t>kwaɪt ə fjuː</t>
         </is>
       </c>
       <c r="E2736" t="inlineStr">
@@ -76254,7 +76259,7 @@
       </c>
       <c r="C2745" t="inlineStr">
         <is>
-          <t>美[nek ənd nek]</t>
+          <t>nek ənd nek</t>
         </is>
       </c>
       <c r="E2745" t="inlineStr">
@@ -76299,7 +76304,7 @@
       </c>
       <c r="C2747" t="inlineStr">
         <is>
-          <t>美[peɪ əˈtenʃn tu]</t>
+          <t>peɪ əˈtenʃn tu</t>
         </is>
       </c>
       <c r="E2747" t="inlineStr">
@@ -76344,7 +76349,7 @@
       </c>
       <c r="C2749" t="inlineStr">
         <is>
-          <t>英[ˈteɪk ɒf] 美[ˈteɪk ɔːf]</t>
+          <t>ˈteɪk ɒf ˈteɪk ɔːf</t>
         </is>
       </c>
       <c r="E2749" t="inlineStr">
@@ -76409,7 +76414,7 @@
       </c>
       <c r="C2752" t="inlineStr">
         <is>
-          <t>美[teɪk aʊt]</t>
+          <t>teɪk aʊt</t>
         </is>
       </c>
       <c r="E2752" t="inlineStr">
@@ -76474,7 +76479,7 @@
       </c>
       <c r="C2755" t="inlineStr">
         <is>
-          <t>美[ðə seɪm æz]</t>
+          <t>ðə seɪm æz</t>
         </is>
       </c>
       <c r="D2755" t="inlineStr">
@@ -76609,7 +76614,7 @@
       </c>
       <c r="C2761" t="inlineStr">
         <is>
-          <t>美[θæŋks tu]</t>
+          <t>θæŋks tu</t>
         </is>
       </c>
       <c r="E2761" t="inlineStr">
@@ -76634,7 +76639,7 @@
       </c>
       <c r="C2762" t="inlineStr">
         <is>
-          <t>美[stɪk tu]</t>
+          <t>stɪk tu</t>
         </is>
       </c>
       <c r="E2762" t="inlineStr">
@@ -76699,7 +76704,7 @@
       </c>
       <c r="C2765" t="inlineStr">
         <is>
-          <t>英[ʃəʊ ɒf]</t>
+          <t>ʃəʊ ɒf</t>
         </is>
       </c>
       <c r="E2765" t="inlineStr">
@@ -76724,7 +76729,7 @@
       </c>
       <c r="C2766" t="inlineStr">
         <is>
-          <t>英[teɪk ə veɪˈkeɪʃn; teɪk ə vəˈkeɪʃn] 美[teɪk ə veɪˈkeɪʃn; teɪk ə vəˈkeɪʃn]</t>
+          <t>teɪk ə veɪˈkeɪʃn; teɪk ə vəˈkeɪʃn</t>
         </is>
       </c>
       <c r="E2766" t="inlineStr">
@@ -76894,7 +76899,7 @@
       </c>
       <c r="C2774" t="inlineStr">
         <is>
-          <t>美[steɪ ʌp]</t>
+          <t>steɪ ʌp</t>
         </is>
       </c>
       <c r="E2774" t="inlineStr">
@@ -76919,7 +76924,7 @@
       </c>
       <c r="C2775" t="inlineStr">
         <is>
-          <t>英[pleɪ wɪð] 美[pleɪ wɪð]</t>
+          <t>pleɪ wɪð</t>
         </is>
       </c>
       <c r="E2775" t="inlineStr">
@@ -76944,7 +76949,7 @@
       </c>
       <c r="C2776" t="inlineStr">
         <is>
-          <t>美[soʊ æz tu]</t>
+          <t>soʊ æz tu</t>
         </is>
       </c>
       <c r="E2776" t="inlineStr">
@@ -77049,7 +77054,7 @@
       </c>
       <c r="C2781" t="inlineStr">
         <is>
-          <t>美[juːz ʌp]</t>
+          <t>juːz ʌp</t>
         </is>
       </c>
       <c r="E2781" t="inlineStr">
@@ -77174,7 +77179,7 @@
       </c>
       <c r="C2787" t="inlineStr">
         <is>
-          <t>英[sʌm ʌp] 美[sʌm ʌp]</t>
+          <t>sʌm ʌp</t>
         </is>
       </c>
       <c r="E2787" t="inlineStr">
@@ -77239,7 +77244,7 @@
       </c>
       <c r="C2790" t="inlineStr">
         <is>
-          <t>英[ˌɒn ˈbɔːd]</t>
+          <t>ˌɒn ˈbɔːd</t>
         </is>
       </c>
       <c r="E2790" t="inlineStr">
@@ -77264,7 +77269,7 @@
       </c>
       <c r="C2791" t="inlineStr">
         <is>
-          <t>美[rɪˈzʌlt frəm]</t>
+          <t>rɪˈzʌlt frəm</t>
         </is>
       </c>
       <c r="E2791" t="inlineStr">
@@ -77309,7 +77314,7 @@
       </c>
       <c r="C2793" t="inlineStr">
         <is>
-          <t>美[jɪr baɪ jɪr]</t>
+          <t>jɪr baɪ jɪr</t>
         </is>
       </c>
       <c r="E2793" t="inlineStr">
@@ -77334,7 +77339,7 @@
       </c>
       <c r="C2794" t="inlineStr">
         <is>
-          <t>美[jɪr ɪn ənd jɪr aʊt]</t>
+          <t>jɪr ɪn ənd jɪr aʊt</t>
         </is>
       </c>
       <c r="E2794" t="inlineStr">
@@ -77419,7 +77424,7 @@
       </c>
       <c r="C2798" t="inlineStr">
         <is>
-          <t>英[pɪk ʌp] 美[pɪk ʌp]</t>
+          <t>pɪk ʌp</t>
         </is>
       </c>
       <c r="E2798" t="inlineStr">
@@ -77544,7 +77549,7 @@
       </c>
       <c r="C2804" t="inlineStr">
         <is>
-          <t>美[səkˈsiːd ɪn]</t>
+          <t>səkˈsiːd ɪn</t>
         </is>
       </c>
       <c r="E2804" t="inlineStr">
@@ -77569,7 +77574,7 @@
       </c>
       <c r="C2805" t="inlineStr">
         <is>
-          <t>美[wɔːk daʊn]</t>
+          <t>wɔːk daʊn</t>
         </is>
       </c>
       <c r="E2805" t="inlineStr">
@@ -77634,7 +77639,7 @@
       </c>
       <c r="C2808" t="inlineStr">
         <is>
-          <t>美[teɪk ə diːp breθ]</t>
+          <t>teɪk ə diːp breθ</t>
         </is>
       </c>
       <c r="E2808" t="inlineStr">
@@ -77699,7 +77704,7 @@
       </c>
       <c r="C2811" t="inlineStr">
         <is>
-          <t>美[tel ðə truːθ]</t>
+          <t>tel ðə truːθ</t>
         </is>
       </c>
       <c r="E2811" t="inlineStr">
@@ -77724,7 +77729,7 @@
       </c>
       <c r="C2812" t="inlineStr">
         <is>
-          <t>美[ʃaʊt æt]</t>
+          <t>ʃaʊt æt</t>
         </is>
       </c>
       <c r="E2812" t="inlineStr">
@@ -77909,7 +77914,7 @@
       </c>
       <c r="C2821" t="inlineStr">
         <is>
-          <t>美[θɪŋk ʌp]</t>
+          <t>θɪŋk ʌp</t>
         </is>
       </c>
       <c r="E2821" t="inlineStr">
@@ -77920,13 +77925,6 @@
       <c r="F2821" t="inlineStr">
         <is>
           <t>n. a. 想出</t>
-        </is>
-      </c>
-    </row>
-    <row r="2822">
-      <c r="A2822" t="inlineStr">
-        <is>
-          <t>中文释义(零基础精简)</t>
         </is>
       </c>
     </row>
